--- a/automation/Test Results/Excel/Appium_Automation_Test_Report.xlsx
+++ b/automation/Test Results/Excel/Appium_Automation_Test_Report.xlsx
@@ -441,7 +441,7 @@
         <v>Medium</v>
       </c>
       <c r="F2">
-        <v>244</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>Medium</v>
       </c>
       <c r="F3">
-        <v>230</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>Medium</v>
       </c>
       <c r="F4">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
         <v>High</v>
       </c>
       <c r="F5">
-        <v>228</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -521,7 +521,7 @@
         <v>Medium</v>
       </c>
       <c r="F6">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +541,7 @@
         <v>Medium</v>
       </c>
       <c r="F7">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -561,7 +561,7 @@
         <v>Medium</v>
       </c>
       <c r="F8">
-        <v>278</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -581,7 +581,7 @@
         <v>High</v>
       </c>
       <c r="F9">
-        <v>163</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -601,7 +601,7 @@
         <v>Medium</v>
       </c>
       <c r="F10">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -621,7 +621,7 @@
         <v>Medium</v>
       </c>
       <c r="F11">
-        <v>201</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -641,7 +641,7 @@
         <v>Medium</v>
       </c>
       <c r="F12">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -661,7 +661,7 @@
         <v>High</v>
       </c>
       <c r="F13">
-        <v>228</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -681,7 +681,7 @@
         <v>Medium</v>
       </c>
       <c r="F14">
-        <v>265</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         <v>Medium</v>
       </c>
       <c r="F15">
-        <v>115</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16">
@@ -721,7 +721,7 @@
         <v>Medium</v>
       </c>
       <c r="F16">
-        <v>267</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         <v>High</v>
       </c>
       <c r="F17">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -761,7 +761,7 @@
         <v>Medium</v>
       </c>
       <c r="F18">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
@@ -781,7 +781,7 @@
         <v>Medium</v>
       </c>
       <c r="F19">
-        <v>187</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20">
@@ -801,7 +801,7 @@
         <v>Medium</v>
       </c>
       <c r="F20">
-        <v>232</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -821,7 +821,7 @@
         <v>High</v>
       </c>
       <c r="F21">
-        <v>247</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -841,7 +841,7 @@
         <v>Medium</v>
       </c>
       <c r="F22">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -861,7 +861,7 @@
         <v>Medium</v>
       </c>
       <c r="F23">
-        <v>133</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24">
@@ -881,7 +881,7 @@
         <v>Medium</v>
       </c>
       <c r="F24">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -901,7 +901,7 @@
         <v>High</v>
       </c>
       <c r="F25">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
@@ -921,7 +921,7 @@
         <v>Medium</v>
       </c>
       <c r="F26">
-        <v>243</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27">
@@ -941,7 +941,7 @@
         <v>Medium</v>
       </c>
       <c r="F27">
-        <v>129</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
@@ -961,7 +961,7 @@
         <v>Medium</v>
       </c>
       <c r="F28">
-        <v>97</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29">
@@ -981,7 +981,7 @@
         <v>High</v>
       </c>
       <c r="F29">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
@@ -1001,7 +1001,7 @@
         <v>Medium</v>
       </c>
       <c r="F30">
-        <v>243</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31">
@@ -1021,7 +1021,7 @@
         <v>Medium</v>
       </c>
       <c r="F31">
-        <v>87</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32">
@@ -1041,7 +1041,7 @@
         <v>Medium</v>
       </c>
       <c r="F32">
-        <v>106</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
@@ -1061,7 +1061,7 @@
         <v>High</v>
       </c>
       <c r="F33">
-        <v>263</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
@@ -1081,7 +1081,7 @@
         <v>Medium</v>
       </c>
       <c r="F34">
-        <v>198</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
@@ -1101,7 +1101,7 @@
         <v>Medium</v>
       </c>
       <c r="F35">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
@@ -1121,7 +1121,7 @@
         <v>Medium</v>
       </c>
       <c r="F36">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
@@ -1141,7 +1141,7 @@
         <v>High</v>
       </c>
       <c r="F37">
-        <v>98</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38">
@@ -1161,7 +1161,7 @@
         <v>Medium</v>
       </c>
       <c r="F38">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39">
@@ -1181,7 +1181,7 @@
         <v>Medium</v>
       </c>
       <c r="F39">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
@@ -1201,7 +1201,7 @@
         <v>Medium</v>
       </c>
       <c r="F40">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
@@ -1221,7 +1221,7 @@
         <v>High</v>
       </c>
       <c r="F41">
-        <v>256</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42">
@@ -1241,7 +1241,7 @@
         <v>Medium</v>
       </c>
       <c r="F42">
-        <v>220</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43">
@@ -1261,7 +1261,7 @@
         <v>Medium</v>
       </c>
       <c r="F43">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44">
@@ -1281,7 +1281,7 @@
         <v>Medium</v>
       </c>
       <c r="F44">
-        <v>206</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
@@ -1301,7 +1301,7 @@
         <v>High</v>
       </c>
       <c r="F45">
-        <v>108</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
@@ -1321,7 +1321,7 @@
         <v>Medium</v>
       </c>
       <c r="F46">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47">
@@ -1341,7 +1341,7 @@
         <v>Medium</v>
       </c>
       <c r="F47">
-        <v>185</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
@@ -1361,7 +1361,7 @@
         <v>Medium</v>
       </c>
       <c r="F48">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
@@ -1381,7 +1381,7 @@
         <v>High</v>
       </c>
       <c r="F49">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50">
@@ -1401,7 +1401,7 @@
         <v>Medium</v>
       </c>
       <c r="F50">
-        <v>92</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51">
@@ -1421,7 +1421,7 @@
         <v>Medium</v>
       </c>
       <c r="F51">
-        <v>197</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52">
@@ -1441,7 +1441,7 @@
         <v>Medium</v>
       </c>
       <c r="F52">
-        <v>253</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53">
@@ -1461,7 +1461,7 @@
         <v>High</v>
       </c>
       <c r="F53">
-        <v>103</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
@@ -1481,7 +1481,7 @@
         <v>Medium</v>
       </c>
       <c r="F54">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55">
@@ -1501,7 +1501,7 @@
         <v>Medium</v>
       </c>
       <c r="F55">
-        <v>257</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56">
@@ -1521,7 +1521,7 @@
         <v>Medium</v>
       </c>
       <c r="F56">
-        <v>262</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57">
@@ -1541,7 +1541,7 @@
         <v>High</v>
       </c>
       <c r="F57">
-        <v>242</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58">
@@ -1561,7 +1561,7 @@
         <v>Medium</v>
       </c>
       <c r="F58">
-        <v>212</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59">
@@ -1581,7 +1581,7 @@
         <v>Medium</v>
       </c>
       <c r="F59">
-        <v>185</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60">
@@ -1601,7 +1601,7 @@
         <v>Medium</v>
       </c>
       <c r="F60">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61">
@@ -1621,7 +1621,7 @@
         <v>High</v>
       </c>
       <c r="F61">
-        <v>258</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62">
@@ -1641,7 +1641,7 @@
         <v>Medium</v>
       </c>
       <c r="F62">
-        <v>239</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63">
@@ -1661,7 +1661,7 @@
         <v>Medium</v>
       </c>
       <c r="F63">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64">
@@ -1681,7 +1681,7 @@
         <v>Medium</v>
       </c>
       <c r="F64">
-        <v>143</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65">
@@ -1701,7 +1701,7 @@
         <v>High</v>
       </c>
       <c r="F65">
-        <v>113</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66">
@@ -1721,7 +1721,7 @@
         <v>Medium</v>
       </c>
       <c r="F66">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
@@ -1741,7 +1741,7 @@
         <v>Medium</v>
       </c>
       <c r="F67">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68">
@@ -1761,7 +1761,7 @@
         <v>Medium</v>
       </c>
       <c r="F68">
-        <v>204</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69">
@@ -1781,7 +1781,7 @@
         <v>High</v>
       </c>
       <c r="F69">
-        <v>142</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70">
@@ -1801,7 +1801,7 @@
         <v>Medium</v>
       </c>
       <c r="F70">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71">
@@ -1821,7 +1821,7 @@
         <v>Medium</v>
       </c>
       <c r="F71">
-        <v>168</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72">
@@ -1841,7 +1841,7 @@
         <v>Medium</v>
       </c>
       <c r="F72">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73">
@@ -1861,7 +1861,7 @@
         <v>Medium</v>
       </c>
       <c r="F73">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74">
@@ -1881,7 +1881,7 @@
         <v>Medium</v>
       </c>
       <c r="F74">
-        <v>148</v>
+        <v>109</v>
       </c>
     </row>
     <row r="75">
@@ -1901,7 +1901,7 @@
         <v>High</v>
       </c>
       <c r="F75">
-        <v>175</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76">
@@ -1921,7 +1921,7 @@
         <v>Medium</v>
       </c>
       <c r="F76">
-        <v>80</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77">
@@ -1941,7 +1941,7 @@
         <v>Medium</v>
       </c>
       <c r="F77">
-        <v>270</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78">
@@ -1961,7 +1961,7 @@
         <v>Medium</v>
       </c>
       <c r="F78">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79">
@@ -1981,7 +1981,7 @@
         <v>High</v>
       </c>
       <c r="F79">
-        <v>110</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80">
@@ -2001,7 +2001,7 @@
         <v>Medium</v>
       </c>
       <c r="F80">
-        <v>255</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81">
@@ -2021,7 +2021,7 @@
         <v>Medium</v>
       </c>
       <c r="F81">
-        <v>88</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82">
@@ -2041,7 +2041,7 @@
         <v>Medium</v>
       </c>
       <c r="F82">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -2061,7 +2061,7 @@
         <v>High</v>
       </c>
       <c r="F83">
-        <v>204</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84">
@@ -2081,7 +2081,7 @@
         <v>Medium</v>
       </c>
       <c r="F84">
-        <v>112</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85">
@@ -2101,7 +2101,7 @@
         <v>Medium</v>
       </c>
       <c r="F85">
-        <v>216</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86">
@@ -2121,7 +2121,7 @@
         <v>Medium</v>
       </c>
       <c r="F86">
-        <v>245</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87">
@@ -2141,7 +2141,7 @@
         <v>High</v>
       </c>
       <c r="F87">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88">
@@ -2161,7 +2161,7 @@
         <v>Medium</v>
       </c>
       <c r="F88">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89">
@@ -2181,7 +2181,7 @@
         <v>Medium</v>
       </c>
       <c r="F89">
-        <v>263</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90">
@@ -2201,7 +2201,7 @@
         <v>Medium</v>
       </c>
       <c r="F90">
-        <v>158</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91">
@@ -2221,7 +2221,7 @@
         <v>High</v>
       </c>
       <c r="F91">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92">
@@ -2241,7 +2241,7 @@
         <v>Medium</v>
       </c>
       <c r="F92">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93">
@@ -2261,7 +2261,7 @@
         <v>Medium</v>
       </c>
       <c r="F93">
-        <v>247</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94">
@@ -2281,7 +2281,7 @@
         <v>Medium</v>
       </c>
       <c r="F94">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95">
@@ -2301,7 +2301,7 @@
         <v>High</v>
       </c>
       <c r="F95">
-        <v>134</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96">
@@ -2321,7 +2321,7 @@
         <v>Medium</v>
       </c>
       <c r="F96">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97">
@@ -2341,7 +2341,7 @@
         <v>Medium</v>
       </c>
       <c r="F97">
-        <v>139</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98">
@@ -2361,7 +2361,7 @@
         <v>Medium</v>
       </c>
       <c r="F98">
-        <v>163</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99">
@@ -2381,7 +2381,7 @@
         <v>High</v>
       </c>
       <c r="F99">
-        <v>173</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100">
@@ -2401,7 +2401,7 @@
         <v>Medium</v>
       </c>
       <c r="F100">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101">
@@ -2421,7 +2421,7 @@
         <v>Medium</v>
       </c>
       <c r="F101">
-        <v>159</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102">
@@ -2461,7 +2461,7 @@
         <v>High</v>
       </c>
       <c r="F103">
-        <v>211</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104">
@@ -2481,7 +2481,7 @@
         <v>Medium</v>
       </c>
       <c r="F104">
-        <v>247</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105">
@@ -2501,7 +2501,7 @@
         <v>Medium</v>
       </c>
       <c r="F105">
-        <v>170</v>
+        <v>119</v>
       </c>
     </row>
     <row r="106">
@@ -2521,7 +2521,7 @@
         <v>Medium</v>
       </c>
       <c r="F106">
-        <v>261</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107">
@@ -2541,7 +2541,7 @@
         <v>High</v>
       </c>
       <c r="F107">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108">
@@ -2561,7 +2561,7 @@
         <v>Medium</v>
       </c>
       <c r="F108">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
@@ -2581,7 +2581,7 @@
         <v>Medium</v>
       </c>
       <c r="F109">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110">
@@ -2601,7 +2601,7 @@
         <v>Medium</v>
       </c>
       <c r="F110">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="111">
@@ -2621,7 +2621,7 @@
         <v>High</v>
       </c>
       <c r="F111">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112">
@@ -2641,7 +2641,7 @@
         <v>Medium</v>
       </c>
       <c r="F112">
-        <v>247</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113">
@@ -2661,7 +2661,7 @@
         <v>Medium</v>
       </c>
       <c r="F113">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114">
@@ -2681,7 +2681,7 @@
         <v>Medium</v>
       </c>
       <c r="F114">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115">
@@ -2701,7 +2701,7 @@
         <v>High</v>
       </c>
       <c r="F115">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116">
@@ -2721,7 +2721,7 @@
         <v>Medium</v>
       </c>
       <c r="F116">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
@@ -2741,7 +2741,7 @@
         <v>Medium</v>
       </c>
       <c r="F117">
-        <v>222</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118">
@@ -2761,7 +2761,7 @@
         <v>Medium</v>
       </c>
       <c r="F118">
-        <v>163</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119">
@@ -2781,7 +2781,7 @@
         <v>High</v>
       </c>
       <c r="F119">
-        <v>107</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120">
@@ -2801,7 +2801,7 @@
         <v>Medium</v>
       </c>
       <c r="F120">
-        <v>275</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121">
@@ -2821,7 +2821,7 @@
         <v>Medium</v>
       </c>
       <c r="F121">
-        <v>171</v>
+        <v>241</v>
       </c>
     </row>
     <row r="122">
@@ -2841,7 +2841,7 @@
         <v>Medium</v>
       </c>
       <c r="F122">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123">
@@ -2861,7 +2861,7 @@
         <v>High</v>
       </c>
       <c r="F123">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="124">
@@ -2881,7 +2881,7 @@
         <v>Medium</v>
       </c>
       <c r="F124">
-        <v>127</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125">
@@ -2901,7 +2901,7 @@
         <v>Medium</v>
       </c>
       <c r="F125">
-        <v>248</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126">
@@ -2921,7 +2921,7 @@
         <v>Medium</v>
       </c>
       <c r="F126">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="127">
@@ -2941,7 +2941,7 @@
         <v>High</v>
       </c>
       <c r="F127">
-        <v>136</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128">
@@ -2961,7 +2961,7 @@
         <v>Medium</v>
       </c>
       <c r="F128">
-        <v>193</v>
+        <v>235</v>
       </c>
     </row>
     <row r="129">
@@ -2981,7 +2981,7 @@
         <v>Medium</v>
       </c>
       <c r="F129">
-        <v>217</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130">
@@ -3001,7 +3001,7 @@
         <v>Medium</v>
       </c>
       <c r="F130">
-        <v>94</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
@@ -3021,7 +3021,7 @@
         <v>High</v>
       </c>
       <c r="F131">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="132">
@@ -3041,7 +3041,7 @@
         <v>Medium</v>
       </c>
       <c r="F132">
-        <v>278</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133">
@@ -3061,7 +3061,7 @@
         <v>Medium</v>
       </c>
       <c r="F133">
-        <v>209</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134">
@@ -3081,7 +3081,7 @@
         <v>Medium</v>
       </c>
       <c r="F134">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135">
@@ -3101,7 +3101,7 @@
         <v>High</v>
       </c>
       <c r="F135">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136">
@@ -3121,7 +3121,7 @@
         <v>Medium</v>
       </c>
       <c r="F136">
-        <v>153</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137">
@@ -3141,7 +3141,7 @@
         <v>Medium</v>
       </c>
       <c r="F137">
-        <v>206</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138">
@@ -3161,7 +3161,7 @@
         <v>Medium</v>
       </c>
       <c r="F138">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139">
@@ -3181,7 +3181,7 @@
         <v>High</v>
       </c>
       <c r="F139">
-        <v>193</v>
+        <v>115</v>
       </c>
     </row>
     <row r="140">
@@ -3201,7 +3201,7 @@
         <v>Medium</v>
       </c>
       <c r="F140">
-        <v>203</v>
+        <v>235</v>
       </c>
     </row>
     <row r="141">
@@ -3221,7 +3221,7 @@
         <v>Medium</v>
       </c>
       <c r="F141">
-        <v>170</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -3241,7 +3241,7 @@
         <v>Medium</v>
       </c>
       <c r="F142">
-        <v>93</v>
+        <v>216</v>
       </c>
     </row>
     <row r="143">
@@ -3261,7 +3261,7 @@
         <v>Medium</v>
       </c>
       <c r="F143">
-        <v>257</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144">
@@ -3281,7 +3281,7 @@
         <v>Medium</v>
       </c>
       <c r="F144">
-        <v>189</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145">
@@ -3301,7 +3301,7 @@
         <v>High</v>
       </c>
       <c r="F145">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
@@ -3321,7 +3321,7 @@
         <v>Medium</v>
       </c>
       <c r="F146">
-        <v>92</v>
+        <v>220</v>
       </c>
     </row>
     <row r="147">
@@ -3341,7 +3341,7 @@
         <v>Medium</v>
       </c>
       <c r="F147">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="148">
@@ -3361,7 +3361,7 @@
         <v>Medium</v>
       </c>
       <c r="F148">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="149">
@@ -3381,7 +3381,7 @@
         <v>High</v>
       </c>
       <c r="F149">
-        <v>178</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150">
@@ -3401,7 +3401,7 @@
         <v>Medium</v>
       </c>
       <c r="F150">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151">
@@ -3421,7 +3421,7 @@
         <v>Medium</v>
       </c>
       <c r="F151">
-        <v>225</v>
+        <v>153</v>
       </c>
     </row>
     <row r="152">
@@ -3441,7 +3441,7 @@
         <v>Medium</v>
       </c>
       <c r="F152">
-        <v>197</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153">
@@ -3461,7 +3461,7 @@
         <v>High</v>
       </c>
       <c r="F153">
-        <v>96</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154">
@@ -3481,7 +3481,7 @@
         <v>Medium</v>
       </c>
       <c r="F154">
-        <v>267</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155">
@@ -3501,7 +3501,7 @@
         <v>Medium</v>
       </c>
       <c r="F155">
-        <v>169</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156">
@@ -3521,7 +3521,7 @@
         <v>Medium</v>
       </c>
       <c r="F156">
-        <v>256</v>
+        <v>84</v>
       </c>
     </row>
     <row r="157">
@@ -3541,7 +3541,7 @@
         <v>High</v>
       </c>
       <c r="F157">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="158">
@@ -3561,7 +3561,7 @@
         <v>Medium</v>
       </c>
       <c r="F158">
-        <v>269</v>
+        <v>148</v>
       </c>
     </row>
     <row r="159">
@@ -3581,7 +3581,7 @@
         <v>Medium</v>
       </c>
       <c r="F159">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160">
@@ -3601,7 +3601,7 @@
         <v>Medium</v>
       </c>
       <c r="F160">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161">
@@ -3621,7 +3621,7 @@
         <v>High</v>
       </c>
       <c r="F161">
-        <v>265</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162">
@@ -3641,7 +3641,7 @@
         <v>Medium</v>
       </c>
       <c r="F162">
-        <v>273</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163">
@@ -3661,7 +3661,7 @@
         <v>Medium</v>
       </c>
       <c r="F163">
-        <v>234</v>
+        <v>102</v>
       </c>
     </row>
     <row r="164">
@@ -3681,7 +3681,7 @@
         <v>Medium</v>
       </c>
       <c r="F164">
-        <v>147</v>
+        <v>241</v>
       </c>
     </row>
     <row r="165">
@@ -3701,7 +3701,7 @@
         <v>High</v>
       </c>
       <c r="F165">
-        <v>111</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166">
@@ -3721,7 +3721,7 @@
         <v>Medium</v>
       </c>
       <c r="F166">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167">
@@ -3741,7 +3741,7 @@
         <v>Medium</v>
       </c>
       <c r="F167">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168">
@@ -3761,7 +3761,7 @@
         <v>Medium</v>
       </c>
       <c r="F168">
-        <v>216</v>
+        <v>263</v>
       </c>
     </row>
     <row r="169">
@@ -3781,7 +3781,7 @@
         <v>High</v>
       </c>
       <c r="F169">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170">
@@ -3801,7 +3801,7 @@
         <v>Medium</v>
       </c>
       <c r="F170">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171">
@@ -3821,7 +3821,7 @@
         <v>Medium</v>
       </c>
       <c r="F171">
-        <v>117</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172">
@@ -3841,7 +3841,7 @@
         <v>Medium</v>
       </c>
       <c r="F172">
-        <v>275</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173">
@@ -3861,7 +3861,7 @@
         <v>High</v>
       </c>
       <c r="F173">
-        <v>240</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174">
@@ -3881,7 +3881,7 @@
         <v>Medium</v>
       </c>
       <c r="F174">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="175">
@@ -3901,7 +3901,7 @@
         <v>Medium</v>
       </c>
       <c r="F175">
-        <v>150</v>
+        <v>271</v>
       </c>
     </row>
     <row r="176">
@@ -3921,7 +3921,7 @@
         <v>Medium</v>
       </c>
       <c r="F176">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177">
@@ -3941,7 +3941,7 @@
         <v>High</v>
       </c>
       <c r="F177">
-        <v>271</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178">
@@ -3961,7 +3961,7 @@
         <v>Medium</v>
       </c>
       <c r="F178">
-        <v>196</v>
+        <v>134</v>
       </c>
     </row>
     <row r="179">
@@ -3981,7 +3981,7 @@
         <v>Medium</v>
       </c>
       <c r="F179">
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180">
@@ -4001,7 +4001,7 @@
         <v>Medium</v>
       </c>
       <c r="F180">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="181">
@@ -4021,7 +4021,7 @@
         <v>High</v>
       </c>
       <c r="F181">
-        <v>115</v>
+        <v>218</v>
       </c>
     </row>
     <row r="182">
@@ -4041,7 +4041,7 @@
         <v>Medium</v>
       </c>
       <c r="F182">
-        <v>96</v>
+        <v>161</v>
       </c>
     </row>
     <row r="183">
@@ -4061,7 +4061,7 @@
         <v>Medium</v>
       </c>
       <c r="F183">
-        <v>140</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184">
@@ -4081,7 +4081,7 @@
         <v>Medium</v>
       </c>
       <c r="F184">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185">
@@ -4101,7 +4101,7 @@
         <v>High</v>
       </c>
       <c r="F185">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="186">
@@ -4121,7 +4121,7 @@
         <v>Medium</v>
       </c>
       <c r="F186">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="187">
@@ -4141,7 +4141,7 @@
         <v>Medium</v>
       </c>
       <c r="F187">
-        <v>139</v>
+        <v>197</v>
       </c>
     </row>
     <row r="188">
@@ -4161,7 +4161,7 @@
         <v>Medium</v>
       </c>
       <c r="F188">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="189">
@@ -4181,7 +4181,7 @@
         <v>High</v>
       </c>
       <c r="F189">
-        <v>254</v>
+        <v>231</v>
       </c>
     </row>
     <row r="190">
@@ -4201,7 +4201,7 @@
         <v>Medium</v>
       </c>
       <c r="F190">
-        <v>219</v>
+        <v>268</v>
       </c>
     </row>
     <row r="191">
@@ -4221,7 +4221,7 @@
         <v>Medium</v>
       </c>
       <c r="F191">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="192">
@@ -4241,7 +4241,7 @@
         <v>Medium</v>
       </c>
       <c r="F192">
-        <v>120</v>
+        <v>181</v>
       </c>
     </row>
     <row r="193">
@@ -4261,7 +4261,7 @@
         <v>High</v>
       </c>
       <c r="F193">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="194">
@@ -4281,7 +4281,7 @@
         <v>Medium</v>
       </c>
       <c r="F194">
-        <v>103</v>
+        <v>157</v>
       </c>
     </row>
     <row r="195">
@@ -4301,7 +4301,7 @@
         <v>Medium</v>
       </c>
       <c r="F195">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="196">
@@ -4321,7 +4321,7 @@
         <v>Medium</v>
       </c>
       <c r="F196">
-        <v>247</v>
+        <v>84</v>
       </c>
     </row>
     <row r="197">
@@ -4341,7 +4341,7 @@
         <v>High</v>
       </c>
       <c r="F197">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="198">
@@ -4361,7 +4361,7 @@
         <v>Medium</v>
       </c>
       <c r="F198">
-        <v>212</v>
+        <v>236</v>
       </c>
     </row>
     <row r="199">
@@ -4381,7 +4381,7 @@
         <v>Medium</v>
       </c>
       <c r="F199">
-        <v>267</v>
+        <v>201</v>
       </c>
     </row>
     <row r="200">
@@ -4401,7 +4401,7 @@
         <v>Medium</v>
       </c>
       <c r="F200">
-        <v>160</v>
+        <v>271</v>
       </c>
     </row>
     <row r="201">
@@ -4421,7 +4421,7 @@
         <v>High</v>
       </c>
       <c r="F201">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="202">
@@ -4441,7 +4441,7 @@
         <v>Medium</v>
       </c>
       <c r="F202">
-        <v>229</v>
+        <v>137</v>
       </c>
     </row>
     <row r="203">
@@ -4461,7 +4461,7 @@
         <v>Medium</v>
       </c>
       <c r="F203">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204">
@@ -4481,7 +4481,7 @@
         <v>Medium</v>
       </c>
       <c r="F204">
-        <v>205</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205">
@@ -4501,7 +4501,7 @@
         <v>High</v>
       </c>
       <c r="F205">
-        <v>178</v>
+        <v>232</v>
       </c>
     </row>
     <row r="206">
@@ -4521,7 +4521,7 @@
         <v>Medium</v>
       </c>
       <c r="F206">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="207">
@@ -4541,7 +4541,7 @@
         <v>Medium</v>
       </c>
       <c r="F207">
-        <v>231</v>
+        <v>102</v>
       </c>
     </row>
     <row r="208">
@@ -4561,7 +4561,7 @@
         <v>Medium</v>
       </c>
       <c r="F208">
-        <v>155</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209">
@@ -4581,7 +4581,7 @@
         <v>High</v>
       </c>
       <c r="F209">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210">
@@ -4601,7 +4601,7 @@
         <v>Medium</v>
       </c>
       <c r="F210">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211">
@@ -4621,7 +4621,7 @@
         <v>Medium</v>
       </c>
       <c r="F211">
-        <v>240</v>
+        <v>87</v>
       </c>
     </row>
     <row r="212">
@@ -4641,7 +4641,7 @@
         <v>Medium</v>
       </c>
       <c r="F212">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="213">
@@ -4661,7 +4661,7 @@
         <v>High</v>
       </c>
       <c r="F213">
-        <v>82</v>
+        <v>141</v>
       </c>
     </row>
     <row r="214">
@@ -4681,7 +4681,7 @@
         <v>Medium</v>
       </c>
       <c r="F214">
-        <v>202</v>
+        <v>94</v>
       </c>
     </row>
     <row r="215">
@@ -4701,7 +4701,7 @@
         <v>Medium</v>
       </c>
       <c r="F215">
-        <v>232</v>
+        <v>112</v>
       </c>
     </row>
     <row r="216">
@@ -4721,7 +4721,7 @@
         <v>Medium</v>
       </c>
       <c r="F216">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="217">
@@ -4741,7 +4741,7 @@
         <v>High</v>
       </c>
       <c r="F217">
-        <v>89</v>
+        <v>162</v>
       </c>
     </row>
     <row r="218">
@@ -4761,7 +4761,7 @@
         <v>Medium</v>
       </c>
       <c r="F218">
-        <v>175</v>
+        <v>85</v>
       </c>
     </row>
     <row r="219">
@@ -4781,7 +4781,7 @@
         <v>Medium</v>
       </c>
       <c r="F219">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="220">
@@ -4801,7 +4801,7 @@
         <v>Medium</v>
       </c>
       <c r="F220">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="221">
@@ -4841,7 +4841,7 @@
         <v>Medium</v>
       </c>
       <c r="F222">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="223">
@@ -4861,7 +4861,7 @@
         <v>Medium</v>
       </c>
       <c r="F223">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="224">
@@ -4881,7 +4881,7 @@
         <v>Medium</v>
       </c>
       <c r="F224">
-        <v>218</v>
+        <v>139</v>
       </c>
     </row>
     <row r="225">
@@ -4901,7 +4901,7 @@
         <v>High</v>
       </c>
       <c r="F225">
-        <v>100</v>
+        <v>212</v>
       </c>
     </row>
     <row r="226">
@@ -4921,7 +4921,7 @@
         <v>Medium</v>
       </c>
       <c r="F226">
-        <v>236</v>
+        <v>195</v>
       </c>
     </row>
     <row r="227">
@@ -4941,7 +4941,7 @@
         <v>Medium</v>
       </c>
       <c r="F227">
-        <v>164</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228">
@@ -4961,7 +4961,7 @@
         <v>Medium</v>
       </c>
       <c r="F228">
-        <v>235</v>
+        <v>176</v>
       </c>
     </row>
     <row r="229">
@@ -4981,7 +4981,7 @@
         <v>High</v>
       </c>
       <c r="F229">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="230">
@@ -5001,7 +5001,7 @@
         <v>Medium</v>
       </c>
       <c r="F230">
-        <v>122</v>
+        <v>177</v>
       </c>
     </row>
     <row r="231">
@@ -5021,7 +5021,7 @@
         <v>Medium</v>
       </c>
       <c r="F231">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="232">
@@ -5041,7 +5041,7 @@
         <v>Medium</v>
       </c>
       <c r="F232">
-        <v>211</v>
+        <v>166</v>
       </c>
     </row>
     <row r="233">
@@ -5061,7 +5061,7 @@
         <v>High</v>
       </c>
       <c r="F233">
-        <v>241</v>
+        <v>275</v>
       </c>
     </row>
     <row r="234">
@@ -5081,7 +5081,7 @@
         <v>Medium</v>
       </c>
       <c r="F234">
-        <v>177</v>
+        <v>82</v>
       </c>
     </row>
     <row r="235">
@@ -5101,7 +5101,7 @@
         <v>Medium</v>
       </c>
       <c r="F235">
-        <v>219</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236">
@@ -5121,7 +5121,7 @@
         <v>Medium</v>
       </c>
       <c r="F236">
-        <v>229</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237">
@@ -5141,7 +5141,7 @@
         <v>High</v>
       </c>
       <c r="F237">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="238">
@@ -5161,7 +5161,7 @@
         <v>Medium</v>
       </c>
       <c r="F238">
-        <v>207</v>
+        <v>120</v>
       </c>
     </row>
     <row r="239">
@@ -5181,7 +5181,7 @@
         <v>Medium</v>
       </c>
       <c r="F239">
-        <v>142</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240">
@@ -5201,7 +5201,7 @@
         <v>Medium</v>
       </c>
       <c r="F240">
-        <v>279</v>
+        <v>232</v>
       </c>
     </row>
     <row r="241">
@@ -5221,7 +5221,7 @@
         <v>High</v>
       </c>
       <c r="F241">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="242">
@@ -5241,7 +5241,7 @@
         <v>Medium</v>
       </c>
       <c r="F242">
-        <v>80</v>
+        <v>186</v>
       </c>
     </row>
     <row r="243">
@@ -5261,7 +5261,7 @@
         <v>Medium</v>
       </c>
       <c r="F243">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="244">
@@ -5281,7 +5281,7 @@
         <v>Medium</v>
       </c>
       <c r="F244">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="245">
@@ -5301,7 +5301,7 @@
         <v>High</v>
       </c>
       <c r="F245">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246">
@@ -5321,7 +5321,7 @@
         <v>Medium</v>
       </c>
       <c r="F246">
-        <v>273</v>
+        <v>213</v>
       </c>
     </row>
     <row r="247">
@@ -5341,7 +5341,7 @@
         <v>Medium</v>
       </c>
       <c r="F247">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248">
@@ -5361,7 +5361,7 @@
         <v>Medium</v>
       </c>
       <c r="F248">
-        <v>120</v>
+        <v>83</v>
       </c>
     </row>
     <row r="249">
@@ -5381,7 +5381,7 @@
         <v>High</v>
       </c>
       <c r="F249">
-        <v>101</v>
+        <v>204</v>
       </c>
     </row>
     <row r="250">
@@ -5401,7 +5401,7 @@
         <v>Medium</v>
       </c>
       <c r="F250">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="251">
@@ -5421,7 +5421,7 @@
         <v>Medium</v>
       </c>
       <c r="F251">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="252">
@@ -5441,7 +5441,7 @@
         <v>Medium</v>
       </c>
       <c r="F252">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="253">
@@ -5461,7 +5461,7 @@
         <v>High</v>
       </c>
       <c r="F253">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="254">
@@ -5481,7 +5481,7 @@
         <v>Medium</v>
       </c>
       <c r="F254">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="255">
@@ -5501,7 +5501,7 @@
         <v>Medium</v>
       </c>
       <c r="F255">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="256">
@@ -5521,7 +5521,7 @@
         <v>Medium</v>
       </c>
       <c r="F256">
-        <v>206</v>
+        <v>86</v>
       </c>
     </row>
     <row r="257">
@@ -5541,7 +5541,7 @@
         <v>High</v>
       </c>
       <c r="F257">
-        <v>216</v>
+        <v>270</v>
       </c>
     </row>
     <row r="258">
@@ -5561,7 +5561,7 @@
         <v>Medium</v>
       </c>
       <c r="F258">
-        <v>275</v>
+        <v>225</v>
       </c>
     </row>
     <row r="259">
@@ -5581,7 +5581,7 @@
         <v>Medium</v>
       </c>
       <c r="F259">
-        <v>123</v>
+        <v>184</v>
       </c>
     </row>
     <row r="260">
@@ -5601,7 +5601,7 @@
         <v>Medium</v>
       </c>
       <c r="F260">
-        <v>262</v>
+        <v>180</v>
       </c>
     </row>
     <row r="261">
@@ -5621,7 +5621,7 @@
         <v>High</v>
       </c>
       <c r="F261">
-        <v>223</v>
+        <v>272</v>
       </c>
     </row>
     <row r="262">
@@ -5641,7 +5641,7 @@
         <v>Medium</v>
       </c>
       <c r="F262">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="263">
@@ -5661,7 +5661,7 @@
         <v>Medium</v>
       </c>
       <c r="F263">
-        <v>189</v>
+        <v>92</v>
       </c>
     </row>
     <row r="264">
@@ -5681,7 +5681,7 @@
         <v>Medium</v>
       </c>
       <c r="F264">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="265">
@@ -5701,7 +5701,7 @@
         <v>High</v>
       </c>
       <c r="F265">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="266">
@@ -5721,7 +5721,7 @@
         <v>Medium</v>
       </c>
       <c r="F266">
-        <v>269</v>
+        <v>246</v>
       </c>
     </row>
     <row r="267">
@@ -5741,7 +5741,7 @@
         <v>Medium</v>
       </c>
       <c r="F267">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="268">
@@ -5761,7 +5761,7 @@
         <v>Medium</v>
       </c>
       <c r="F268">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="269">
@@ -5781,7 +5781,7 @@
         <v>High</v>
       </c>
       <c r="F269">
-        <v>210</v>
+        <v>161</v>
       </c>
     </row>
     <row r="270">
@@ -5801,7 +5801,7 @@
         <v>Medium</v>
       </c>
       <c r="F270">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="271">
@@ -5821,7 +5821,7 @@
         <v>Medium</v>
       </c>
       <c r="F271">
-        <v>238</v>
+        <v>171</v>
       </c>
     </row>
     <row r="272">
@@ -5841,7 +5841,7 @@
         <v>Medium</v>
       </c>
       <c r="F272">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="273">
@@ -5861,7 +5861,7 @@
         <v>High</v>
       </c>
       <c r="F273">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="274">
@@ -5881,7 +5881,7 @@
         <v>Medium</v>
       </c>
       <c r="F274">
-        <v>273</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275">
@@ -5901,7 +5901,7 @@
         <v>Medium</v>
       </c>
       <c r="F275">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="276">
@@ -5921,7 +5921,7 @@
         <v>Medium</v>
       </c>
       <c r="F276">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="277">
@@ -5941,7 +5941,7 @@
         <v>High</v>
       </c>
       <c r="F277">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="278">
@@ -5961,7 +5961,7 @@
         <v>Medium</v>
       </c>
       <c r="F278">
-        <v>233</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279">
@@ -5981,7 +5981,7 @@
         <v>Medium</v>
       </c>
       <c r="F279">
-        <v>210</v>
+        <v>116</v>
       </c>
     </row>
     <row r="280">
@@ -6001,7 +6001,7 @@
         <v>Medium</v>
       </c>
       <c r="F280">
-        <v>217</v>
+        <v>88</v>
       </c>
     </row>
     <row r="281">
@@ -6021,7 +6021,7 @@
         <v>High</v>
       </c>
       <c r="F281">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="282">
@@ -6041,7 +6041,7 @@
         <v>Medium</v>
       </c>
       <c r="F282">
-        <v>155</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283">
@@ -6061,7 +6061,7 @@
         <v>Medium</v>
       </c>
       <c r="F283">
-        <v>270</v>
+        <v>202</v>
       </c>
     </row>
     <row r="284">
@@ -6081,7 +6081,7 @@
         <v>Medium</v>
       </c>
       <c r="F284">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="285">
@@ -6101,7 +6101,7 @@
         <v>High</v>
       </c>
       <c r="F285">
-        <v>274</v>
+        <v>160</v>
       </c>
     </row>
     <row r="286">
@@ -6121,7 +6121,7 @@
         <v>Medium</v>
       </c>
       <c r="F286">
-        <v>221</v>
+        <v>127</v>
       </c>
     </row>
     <row r="287">
@@ -6141,7 +6141,7 @@
         <v>Medium</v>
       </c>
       <c r="F287">
-        <v>121</v>
+        <v>240</v>
       </c>
     </row>
     <row r="288">
@@ -6161,7 +6161,7 @@
         <v>Medium</v>
       </c>
       <c r="F288">
-        <v>237</v>
+        <v>99</v>
       </c>
     </row>
     <row r="289">
@@ -6181,7 +6181,7 @@
         <v>High</v>
       </c>
       <c r="F289">
-        <v>239</v>
+        <v>175</v>
       </c>
     </row>
     <row r="290">
@@ -6201,7 +6201,7 @@
         <v>Medium</v>
       </c>
       <c r="F290">
-        <v>248</v>
+        <v>195</v>
       </c>
     </row>
     <row r="291">
@@ -6221,7 +6221,7 @@
         <v>Medium</v>
       </c>
       <c r="F291">
-        <v>140</v>
+        <v>184</v>
       </c>
     </row>
     <row r="292">
@@ -6241,7 +6241,7 @@
         <v>Medium</v>
       </c>
       <c r="F292">
-        <v>149</v>
+        <v>89</v>
       </c>
     </row>
     <row r="293">
@@ -6261,7 +6261,7 @@
         <v>High</v>
       </c>
       <c r="F293">
-        <v>121</v>
+        <v>276</v>
       </c>
     </row>
     <row r="294">
@@ -6281,7 +6281,7 @@
         <v>Medium</v>
       </c>
       <c r="F294">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="295">
@@ -6301,7 +6301,7 @@
         <v>Medium</v>
       </c>
       <c r="F295">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="296">
@@ -6321,7 +6321,7 @@
         <v>Medium</v>
       </c>
       <c r="F296">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="297">
@@ -6341,7 +6341,7 @@
         <v>High</v>
       </c>
       <c r="F297">
-        <v>273</v>
+        <v>156</v>
       </c>
     </row>
     <row r="298">
@@ -6361,7 +6361,7 @@
         <v>Medium</v>
       </c>
       <c r="F298">
-        <v>113</v>
+        <v>241</v>
       </c>
     </row>
     <row r="299">
@@ -6381,7 +6381,7 @@
         <v>Medium</v>
       </c>
       <c r="F299">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="300">
@@ -6401,7 +6401,7 @@
         <v>Medium</v>
       </c>
       <c r="F300">
-        <v>274</v>
+        <v>148</v>
       </c>
     </row>
     <row r="301">
@@ -6421,7 +6421,7 @@
         <v>High</v>
       </c>
       <c r="F301">
-        <v>225</v>
+        <v>198</v>
       </c>
     </row>
     <row r="302">
@@ -6441,7 +6441,7 @@
         <v>Medium</v>
       </c>
       <c r="F302">
-        <v>143</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303">
@@ -6461,7 +6461,7 @@
         <v>Medium</v>
       </c>
       <c r="F303">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="304">
@@ -6481,7 +6481,7 @@
         <v>Medium</v>
       </c>
       <c r="F304">
-        <v>275</v>
+        <v>224</v>
       </c>
     </row>
     <row r="305">
@@ -6501,7 +6501,7 @@
         <v>High</v>
       </c>
       <c r="F305">
-        <v>184</v>
+        <v>255</v>
       </c>
     </row>
     <row r="306">
@@ -6521,7 +6521,7 @@
         <v>Medium</v>
       </c>
       <c r="F306">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="307">
@@ -6541,7 +6541,7 @@
         <v>Medium</v>
       </c>
       <c r="F307">
-        <v>200</v>
+        <v>246</v>
       </c>
     </row>
     <row r="308">
@@ -6561,7 +6561,7 @@
         <v>Medium</v>
       </c>
       <c r="F308">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="309">
@@ -6581,7 +6581,7 @@
         <v>High</v>
       </c>
       <c r="F309">
-        <v>227</v>
+        <v>113</v>
       </c>
     </row>
     <row r="310">
@@ -6601,7 +6601,7 @@
         <v>Medium</v>
       </c>
       <c r="F310">
-        <v>263</v>
+        <v>115</v>
       </c>
     </row>
     <row r="311">
@@ -6621,7 +6621,7 @@
         <v>Medium</v>
       </c>
       <c r="F311">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="312">
@@ -6641,7 +6641,7 @@
         <v>Medium</v>
       </c>
       <c r="F312">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
     <row r="313">
@@ -6661,7 +6661,7 @@
         <v>High</v>
       </c>
       <c r="F313">
-        <v>221</v>
+        <v>260</v>
       </c>
     </row>
     <row r="314">
@@ -6681,7 +6681,7 @@
         <v>Medium</v>
       </c>
       <c r="F314">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="315">
@@ -6701,7 +6701,7 @@
         <v>Medium</v>
       </c>
       <c r="F315">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="316">
@@ -6721,7 +6721,7 @@
         <v>Medium</v>
       </c>
       <c r="F316">
-        <v>107</v>
+        <v>201</v>
       </c>
     </row>
     <row r="317">
@@ -6741,7 +6741,7 @@
         <v>High</v>
       </c>
       <c r="F317">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="318">
@@ -6761,7 +6761,7 @@
         <v>Medium</v>
       </c>
       <c r="F318">
-        <v>225</v>
+        <v>257</v>
       </c>
     </row>
     <row r="319">
@@ -6781,7 +6781,7 @@
         <v>Medium</v>
       </c>
       <c r="F319">
-        <v>208</v>
+        <v>259</v>
       </c>
     </row>
     <row r="320">
@@ -6801,7 +6801,7 @@
         <v>Medium</v>
       </c>
       <c r="F320">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="321">
@@ -6821,7 +6821,7 @@
         <v>High</v>
       </c>
       <c r="F321">
-        <v>233</v>
+        <v>179</v>
       </c>
     </row>
     <row r="322">
@@ -6841,7 +6841,7 @@
         <v>Medium</v>
       </c>
       <c r="F322">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="323">
@@ -6861,7 +6861,7 @@
         <v>Medium</v>
       </c>
       <c r="F323">
-        <v>201</v>
+        <v>158</v>
       </c>
     </row>
     <row r="324">
@@ -6881,7 +6881,7 @@
         <v>Medium</v>
       </c>
       <c r="F324">
-        <v>134</v>
+        <v>198</v>
       </c>
     </row>
     <row r="325">
@@ -6901,7 +6901,7 @@
         <v>High</v>
       </c>
       <c r="F325">
-        <v>217</v>
+        <v>173</v>
       </c>
     </row>
     <row r="326">
@@ -6921,7 +6921,7 @@
         <v>Medium</v>
       </c>
       <c r="F326">
-        <v>204</v>
+        <v>273</v>
       </c>
     </row>
     <row r="327">
@@ -6941,7 +6941,7 @@
         <v>Medium</v>
       </c>
       <c r="F327">
-        <v>242</v>
+        <v>138</v>
       </c>
     </row>
     <row r="328">
@@ -6961,7 +6961,7 @@
         <v>Medium</v>
       </c>
       <c r="F328">
-        <v>248</v>
+        <v>102</v>
       </c>
     </row>
     <row r="329">
@@ -6981,7 +6981,7 @@
         <v>High</v>
       </c>
       <c r="F329">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="330">
@@ -7001,7 +7001,7 @@
         <v>Medium</v>
       </c>
       <c r="F330">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="331">
@@ -7021,7 +7021,7 @@
         <v>Medium</v>
       </c>
       <c r="F331">
-        <v>176</v>
+        <v>151</v>
       </c>
     </row>
     <row r="332">
@@ -7041,7 +7041,7 @@
         <v>Medium</v>
       </c>
       <c r="F332">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="333">
@@ -7061,7 +7061,7 @@
         <v>High</v>
       </c>
       <c r="F333">
-        <v>82</v>
+        <v>186</v>
       </c>
     </row>
     <row r="334">
@@ -7081,7 +7081,7 @@
         <v>Medium</v>
       </c>
       <c r="F334">
-        <v>206</v>
+        <v>252</v>
       </c>
     </row>
     <row r="335">
@@ -7101,7 +7101,7 @@
         <v>Medium</v>
       </c>
       <c r="F335">
-        <v>107</v>
+        <v>255</v>
       </c>
     </row>
     <row r="336">
@@ -7121,7 +7121,7 @@
         <v>Medium</v>
       </c>
       <c r="F336">
-        <v>179</v>
+        <v>103</v>
       </c>
     </row>
     <row r="337">
@@ -7141,7 +7141,7 @@
         <v>High</v>
       </c>
       <c r="F337">
-        <v>213</v>
+        <v>175</v>
       </c>
     </row>
     <row r="338">
@@ -7161,7 +7161,7 @@
         <v>Medium</v>
       </c>
       <c r="F338">
-        <v>96</v>
+        <v>238</v>
       </c>
     </row>
     <row r="339">
@@ -7181,7 +7181,7 @@
         <v>Medium</v>
       </c>
       <c r="F339">
-        <v>98</v>
+        <v>253</v>
       </c>
     </row>
     <row r="340">
@@ -7201,7 +7201,7 @@
         <v>Medium</v>
       </c>
       <c r="F340">
-        <v>158</v>
+        <v>192</v>
       </c>
     </row>
     <row r="341">
@@ -7221,7 +7221,7 @@
         <v>High</v>
       </c>
       <c r="F341">
-        <v>260</v>
+        <v>173</v>
       </c>
     </row>
     <row r="342">
@@ -7241,7 +7241,7 @@
         <v>Medium</v>
       </c>
       <c r="F342">
-        <v>247</v>
+        <v>226</v>
       </c>
     </row>
     <row r="343">
@@ -7261,7 +7261,7 @@
         <v>Medium</v>
       </c>
       <c r="F343">
-        <v>95</v>
+        <v>221</v>
       </c>
     </row>
     <row r="344">
@@ -7281,7 +7281,7 @@
         <v>Medium</v>
       </c>
       <c r="F344">
-        <v>275</v>
+        <v>106</v>
       </c>
     </row>
     <row r="345">
@@ -7301,7 +7301,7 @@
         <v>High</v>
       </c>
       <c r="F345">
-        <v>110</v>
+        <v>221</v>
       </c>
     </row>
     <row r="346">
@@ -7321,7 +7321,7 @@
         <v>Medium</v>
       </c>
       <c r="F346">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="347">
@@ -7341,7 +7341,7 @@
         <v>Medium</v>
       </c>
       <c r="F347">
-        <v>271</v>
+        <v>166</v>
       </c>
     </row>
     <row r="348">
@@ -7361,7 +7361,7 @@
         <v>Medium</v>
       </c>
       <c r="F348">
-        <v>81</v>
+        <v>188</v>
       </c>
     </row>
     <row r="349">
@@ -7381,7 +7381,7 @@
         <v>High</v>
       </c>
       <c r="F349">
-        <v>113</v>
+        <v>202</v>
       </c>
     </row>
     <row r="350">
@@ -7401,7 +7401,7 @@
         <v>Medium</v>
       </c>
       <c r="F350">
-        <v>146</v>
+        <v>109</v>
       </c>
     </row>
     <row r="351">
@@ -7421,7 +7421,7 @@
         <v>Medium</v>
       </c>
       <c r="F351">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="352">
@@ -7441,7 +7441,7 @@
         <v>Medium</v>
       </c>
       <c r="F352">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="353">
@@ -7461,7 +7461,7 @@
         <v>High</v>
       </c>
       <c r="F353">
-        <v>269</v>
+        <v>166</v>
       </c>
     </row>
     <row r="354">
@@ -7481,7 +7481,7 @@
         <v>Medium</v>
       </c>
       <c r="F354">
-        <v>245</v>
+        <v>154</v>
       </c>
     </row>
     <row r="355">
@@ -7501,7 +7501,7 @@
         <v>Medium</v>
       </c>
       <c r="F355">
-        <v>157</v>
+        <v>110</v>
       </c>
     </row>
     <row r="356">
@@ -7521,7 +7521,7 @@
         <v>Medium</v>
       </c>
       <c r="F356">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="357">
@@ -7541,7 +7541,7 @@
         <v>High</v>
       </c>
       <c r="F357">
-        <v>245</v>
+        <v>143</v>
       </c>
     </row>
     <row r="358">
@@ -7561,7 +7561,7 @@
         <v>Medium</v>
       </c>
       <c r="F358">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="359">
@@ -7581,7 +7581,7 @@
         <v>Medium</v>
       </c>
       <c r="F359">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="360">
@@ -7601,7 +7601,7 @@
         <v>Medium</v>
       </c>
       <c r="F360">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="361">
@@ -7621,7 +7621,7 @@
         <v>High</v>
       </c>
       <c r="F361">
-        <v>277</v>
+        <v>245</v>
       </c>
     </row>
     <row r="362">
@@ -7641,7 +7641,7 @@
         <v>Medium</v>
       </c>
       <c r="F362">
-        <v>118</v>
+        <v>195</v>
       </c>
     </row>
     <row r="363">
@@ -7661,7 +7661,7 @@
         <v>Medium</v>
       </c>
       <c r="F363">
-        <v>95</v>
+        <v>200</v>
       </c>
     </row>
     <row r="364">
@@ -7681,7 +7681,7 @@
         <v>Medium</v>
       </c>
       <c r="F364">
-        <v>204</v>
+        <v>121</v>
       </c>
     </row>
     <row r="365">
@@ -7701,7 +7701,7 @@
         <v>High</v>
       </c>
       <c r="F365">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="366">
@@ -7721,7 +7721,7 @@
         <v>Medium</v>
       </c>
       <c r="F366">
-        <v>211</v>
+        <v>101</v>
       </c>
     </row>
     <row r="367">
@@ -7741,7 +7741,7 @@
         <v>Medium</v>
       </c>
       <c r="F367">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="368">
@@ -7761,7 +7761,7 @@
         <v>Medium</v>
       </c>
       <c r="F368">
-        <v>249</v>
+        <v>128</v>
       </c>
     </row>
     <row r="369">
@@ -7781,7 +7781,7 @@
         <v>High</v>
       </c>
       <c r="F369">
-        <v>203</v>
+        <v>232</v>
       </c>
     </row>
     <row r="370">
@@ -7801,7 +7801,7 @@
         <v>Medium</v>
       </c>
       <c r="F370">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="371">
@@ -7821,7 +7821,7 @@
         <v>Medium</v>
       </c>
       <c r="F371">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="372">
@@ -7841,7 +7841,7 @@
         <v>Medium</v>
       </c>
       <c r="F372">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="373">
@@ -7861,7 +7861,7 @@
         <v>High</v>
       </c>
       <c r="F373">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="374">
@@ -7881,7 +7881,7 @@
         <v>Medium</v>
       </c>
       <c r="F374">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="375">
@@ -7921,7 +7921,7 @@
         <v>Medium</v>
       </c>
       <c r="F376">
-        <v>105</v>
+        <v>248</v>
       </c>
     </row>
     <row r="377">
@@ -7941,7 +7941,7 @@
         <v>High</v>
       </c>
       <c r="F377">
-        <v>175</v>
+        <v>246</v>
       </c>
     </row>
     <row r="378">
@@ -7961,7 +7961,7 @@
         <v>Medium</v>
       </c>
       <c r="F378">
-        <v>159</v>
+        <v>276</v>
       </c>
     </row>
     <row r="379">
@@ -7981,7 +7981,7 @@
         <v>Medium</v>
       </c>
       <c r="F379">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380">
@@ -8001,7 +8001,7 @@
         <v>Medium</v>
       </c>
       <c r="F380">
-        <v>173</v>
+        <v>216</v>
       </c>
     </row>
     <row r="381">
@@ -8021,7 +8021,7 @@
         <v>High</v>
       </c>
       <c r="F381">
-        <v>150</v>
+        <v>192</v>
       </c>
     </row>
     <row r="382">
@@ -8041,7 +8041,7 @@
         <v>Medium</v>
       </c>
       <c r="F382">
-        <v>252</v>
+        <v>233</v>
       </c>
     </row>
     <row r="383">
@@ -8061,7 +8061,7 @@
         <v>Medium</v>
       </c>
       <c r="F383">
-        <v>110</v>
+        <v>251</v>
       </c>
     </row>
     <row r="384">
@@ -8081,7 +8081,7 @@
         <v>Medium</v>
       </c>
       <c r="F384">
-        <v>125</v>
+        <v>174</v>
       </c>
     </row>
     <row r="385">
@@ -8101,7 +8101,7 @@
         <v>High</v>
       </c>
       <c r="F385">
-        <v>116</v>
+        <v>255</v>
       </c>
     </row>
     <row r="386">
@@ -8121,7 +8121,7 @@
         <v>Medium</v>
       </c>
       <c r="F386">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="387">
@@ -8141,7 +8141,7 @@
         <v>Medium</v>
       </c>
       <c r="F387">
-        <v>137</v>
+        <v>262</v>
       </c>
     </row>
     <row r="388">
@@ -8161,7 +8161,7 @@
         <v>Medium</v>
       </c>
       <c r="F388">
-        <v>276</v>
+        <v>145</v>
       </c>
     </row>
     <row r="389">
@@ -8181,7 +8181,7 @@
         <v>High</v>
       </c>
       <c r="F389">
-        <v>215</v>
+        <v>250</v>
       </c>
     </row>
     <row r="390">
@@ -8201,7 +8201,7 @@
         <v>Medium</v>
       </c>
       <c r="F390">
-        <v>237</v>
+        <v>120</v>
       </c>
     </row>
     <row r="391">
@@ -8221,7 +8221,7 @@
         <v>Medium</v>
       </c>
       <c r="F391">
-        <v>246</v>
+        <v>92</v>
       </c>
     </row>
     <row r="392">
@@ -8241,7 +8241,7 @@
         <v>Medium</v>
       </c>
       <c r="F392">
-        <v>164</v>
+        <v>250</v>
       </c>
     </row>
     <row r="393">
@@ -8261,7 +8261,7 @@
         <v>High</v>
       </c>
       <c r="F393">
-        <v>242</v>
+        <v>159</v>
       </c>
     </row>
     <row r="394">
@@ -8281,7 +8281,7 @@
         <v>Medium</v>
       </c>
       <c r="F394">
-        <v>145</v>
+        <v>259</v>
       </c>
     </row>
     <row r="395">
@@ -8301,7 +8301,7 @@
         <v>Medium</v>
       </c>
       <c r="F395">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="396">
@@ -8321,7 +8321,7 @@
         <v>Medium</v>
       </c>
       <c r="F396">
-        <v>175</v>
+        <v>275</v>
       </c>
     </row>
     <row r="397">
@@ -8341,7 +8341,7 @@
         <v>High</v>
       </c>
       <c r="F397">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="398">
@@ -8361,7 +8361,7 @@
         <v>Medium</v>
       </c>
       <c r="F398">
-        <v>165</v>
+        <v>251</v>
       </c>
     </row>
     <row r="399">
@@ -8381,7 +8381,7 @@
         <v>Medium</v>
       </c>
       <c r="F399">
-        <v>254</v>
+        <v>175</v>
       </c>
     </row>
     <row r="400">
@@ -8401,7 +8401,7 @@
         <v>Medium</v>
       </c>
       <c r="F400">
-        <v>196</v>
+        <v>255</v>
       </c>
     </row>
     <row r="401">
@@ -8421,7 +8421,7 @@
         <v>High</v>
       </c>
       <c r="F401">
-        <v>242</v>
+        <v>213</v>
       </c>
     </row>
     <row r="402">
@@ -8441,7 +8441,7 @@
         <v>Medium</v>
       </c>
       <c r="F402">
-        <v>244</v>
+        <v>116</v>
       </c>
     </row>
     <row r="403">
@@ -8461,7 +8461,7 @@
         <v>Medium</v>
       </c>
       <c r="F403">
-        <v>257</v>
+        <v>159</v>
       </c>
     </row>
     <row r="404">
@@ -8481,7 +8481,7 @@
         <v>Medium</v>
       </c>
       <c r="F404">
-        <v>224</v>
+        <v>143</v>
       </c>
     </row>
     <row r="405">
@@ -8501,7 +8501,7 @@
         <v>High</v>
       </c>
       <c r="F405">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="406">
@@ -8521,7 +8521,7 @@
         <v>Medium</v>
       </c>
       <c r="F406">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="407">
@@ -8541,7 +8541,7 @@
         <v>Medium</v>
       </c>
       <c r="F407">
-        <v>242</v>
+        <v>109</v>
       </c>
     </row>
     <row r="408">
@@ -8561,7 +8561,7 @@
         <v>Medium</v>
       </c>
       <c r="F408">
-        <v>221</v>
+        <v>192</v>
       </c>
     </row>
     <row r="409">
@@ -8581,7 +8581,7 @@
         <v>High</v>
       </c>
       <c r="F409">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="410">
@@ -8601,7 +8601,7 @@
         <v>Medium</v>
       </c>
       <c r="F410">
-        <v>92</v>
+        <v>148</v>
       </c>
     </row>
     <row r="411">
@@ -8621,7 +8621,7 @@
         <v>Medium</v>
       </c>
       <c r="F411">
-        <v>103</v>
+        <v>235</v>
       </c>
     </row>
     <row r="412">
@@ -8641,7 +8641,7 @@
         <v>Medium</v>
       </c>
       <c r="F412">
-        <v>242</v>
+        <v>187</v>
       </c>
     </row>
     <row r="413">
@@ -8661,7 +8661,7 @@
         <v>Medium</v>
       </c>
       <c r="F413">
-        <v>237</v>
+        <v>146</v>
       </c>
     </row>
     <row r="414">
@@ -8681,7 +8681,7 @@
         <v>Medium</v>
       </c>
       <c r="F414">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="415">
@@ -8701,7 +8701,7 @@
         <v>High</v>
       </c>
       <c r="F415">
-        <v>187</v>
+        <v>233</v>
       </c>
     </row>
     <row r="416">
@@ -8721,7 +8721,7 @@
         <v>Medium</v>
       </c>
       <c r="F416">
-        <v>197</v>
+        <v>99</v>
       </c>
     </row>
     <row r="417">
@@ -8741,7 +8741,7 @@
         <v>Medium</v>
       </c>
       <c r="F417">
-        <v>163</v>
+        <v>230</v>
       </c>
     </row>
     <row r="418">
@@ -8761,7 +8761,7 @@
         <v>Medium</v>
       </c>
       <c r="F418">
-        <v>243</v>
+        <v>116</v>
       </c>
     </row>
     <row r="419">
@@ -8781,7 +8781,7 @@
         <v>High</v>
       </c>
       <c r="F419">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="420">
@@ -8801,7 +8801,7 @@
         <v>Medium</v>
       </c>
       <c r="F420">
-        <v>240</v>
+        <v>93</v>
       </c>
     </row>
     <row r="421">
@@ -8821,7 +8821,7 @@
         <v>Medium</v>
       </c>
       <c r="F421">
-        <v>137</v>
+        <v>223</v>
       </c>
     </row>
     <row r="422">
@@ -8841,7 +8841,7 @@
         <v>Medium</v>
       </c>
       <c r="F422">
-        <v>196</v>
+        <v>94</v>
       </c>
     </row>
     <row r="423">
@@ -8861,7 +8861,7 @@
         <v>High</v>
       </c>
       <c r="F423">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="424">
@@ -8881,7 +8881,7 @@
         <v>Medium</v>
       </c>
       <c r="F424">
-        <v>237</v>
+        <v>174</v>
       </c>
     </row>
     <row r="425">
@@ -8901,7 +8901,7 @@
         <v>Medium</v>
       </c>
       <c r="F425">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="426">
@@ -8921,7 +8921,7 @@
         <v>Medium</v>
       </c>
       <c r="F426">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="427">
@@ -8941,7 +8941,7 @@
         <v>High</v>
       </c>
       <c r="F427">
-        <v>163</v>
+        <v>226</v>
       </c>
     </row>
     <row r="428">
@@ -8961,7 +8961,7 @@
         <v>Medium</v>
       </c>
       <c r="F428">
-        <v>179</v>
+        <v>124</v>
       </c>
     </row>
     <row r="429">
@@ -8981,7 +8981,7 @@
         <v>Medium</v>
       </c>
       <c r="F429">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="430">
@@ -9001,7 +9001,7 @@
         <v>Medium</v>
       </c>
       <c r="F430">
-        <v>149</v>
+        <v>225</v>
       </c>
     </row>
     <row r="431">
@@ -9021,7 +9021,7 @@
         <v>High</v>
       </c>
       <c r="F431">
-        <v>132</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432">
@@ -9041,7 +9041,7 @@
         <v>Medium</v>
       </c>
       <c r="F432">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="433">
@@ -9061,7 +9061,7 @@
         <v>Medium</v>
       </c>
       <c r="F433">
-        <v>163</v>
+        <v>235</v>
       </c>
     </row>
     <row r="434">
@@ -9081,7 +9081,7 @@
         <v>Medium</v>
       </c>
       <c r="F434">
-        <v>264</v>
+        <v>165</v>
       </c>
     </row>
     <row r="435">
@@ -9101,7 +9101,7 @@
         <v>High</v>
       </c>
       <c r="F435">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="436">
@@ -9121,7 +9121,7 @@
         <v>Medium</v>
       </c>
       <c r="F436">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="437">
@@ -9141,7 +9141,7 @@
         <v>Medium</v>
       </c>
       <c r="F437">
-        <v>162</v>
+        <v>199</v>
       </c>
     </row>
     <row r="438">
@@ -9161,7 +9161,7 @@
         <v>Medium</v>
       </c>
       <c r="F438">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="439">
@@ -9181,7 +9181,7 @@
         <v>High</v>
       </c>
       <c r="F439">
-        <v>157</v>
+        <v>251</v>
       </c>
     </row>
     <row r="440">
@@ -9201,7 +9201,7 @@
         <v>Medium</v>
       </c>
       <c r="F440">
-        <v>210</v>
+        <v>123</v>
       </c>
     </row>
     <row r="441">
@@ -9221,7 +9221,7 @@
         <v>Medium</v>
       </c>
       <c r="F441">
-        <v>212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="442">
@@ -9241,7 +9241,7 @@
         <v>Medium</v>
       </c>
       <c r="F442">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="443">
@@ -9261,7 +9261,7 @@
         <v>Medium</v>
       </c>
       <c r="F443">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="444">
@@ -9281,7 +9281,7 @@
         <v>Medium</v>
       </c>
       <c r="F444">
-        <v>208</v>
+        <v>138</v>
       </c>
     </row>
     <row r="445">
@@ -9301,7 +9301,7 @@
         <v>High</v>
       </c>
       <c r="F445">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="446">
@@ -9321,7 +9321,7 @@
         <v>Medium</v>
       </c>
       <c r="F446">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="447">
@@ -9341,7 +9341,7 @@
         <v>Medium</v>
       </c>
       <c r="F447">
-        <v>217</v>
+        <v>261</v>
       </c>
     </row>
     <row r="448">
@@ -9361,7 +9361,7 @@
         <v>Medium</v>
       </c>
       <c r="F448">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="449">
@@ -9381,7 +9381,7 @@
         <v>High</v>
       </c>
       <c r="F449">
-        <v>112</v>
+        <v>271</v>
       </c>
     </row>
     <row r="450">
@@ -9401,7 +9401,7 @@
         <v>Medium</v>
       </c>
       <c r="F450">
-        <v>196</v>
+        <v>241</v>
       </c>
     </row>
     <row r="451">
@@ -9421,7 +9421,7 @@
         <v>Medium</v>
       </c>
       <c r="F451">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452">
@@ -9441,7 +9441,7 @@
         <v>Medium</v>
       </c>
       <c r="F452">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="453">
@@ -9461,7 +9461,7 @@
         <v>High</v>
       </c>
       <c r="F453">
-        <v>182</v>
+        <v>229</v>
       </c>
     </row>
     <row r="454">
@@ -9481,7 +9481,7 @@
         <v>Medium</v>
       </c>
       <c r="F454">
-        <v>198</v>
+        <v>106</v>
       </c>
     </row>
     <row r="455">
@@ -9501,7 +9501,7 @@
         <v>Medium</v>
       </c>
       <c r="F455">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="456">
@@ -9521,7 +9521,7 @@
         <v>Medium</v>
       </c>
       <c r="F456">
-        <v>145</v>
+        <v>220</v>
       </c>
     </row>
     <row r="457">
@@ -9541,7 +9541,7 @@
         <v>High</v>
       </c>
       <c r="F457">
-        <v>101</v>
+        <v>198</v>
       </c>
     </row>
     <row r="458">
@@ -9561,7 +9561,7 @@
         <v>Medium</v>
       </c>
       <c r="F458">
-        <v>276</v>
+        <v>218</v>
       </c>
     </row>
     <row r="459">
@@ -9581,7 +9581,7 @@
         <v>Medium</v>
       </c>
       <c r="F459">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="460">
@@ -9601,7 +9601,7 @@
         <v>Medium</v>
       </c>
       <c r="F460">
-        <v>275</v>
+        <v>241</v>
       </c>
     </row>
     <row r="461">
@@ -9621,7 +9621,7 @@
         <v>High</v>
       </c>
       <c r="F461">
-        <v>164</v>
+        <v>219</v>
       </c>
     </row>
     <row r="462">
@@ -9641,7 +9641,7 @@
         <v>Medium</v>
       </c>
       <c r="F462">
-        <v>220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="463">
@@ -9661,7 +9661,7 @@
         <v>Medium</v>
       </c>
       <c r="F463">
-        <v>239</v>
+        <v>107</v>
       </c>
     </row>
     <row r="464">
@@ -9681,7 +9681,7 @@
         <v>Medium</v>
       </c>
       <c r="F464">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="465">
@@ -9701,7 +9701,7 @@
         <v>High</v>
       </c>
       <c r="F465">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="466">
@@ -9721,7 +9721,7 @@
         <v>Medium</v>
       </c>
       <c r="F466">
-        <v>87</v>
+        <v>182</v>
       </c>
     </row>
     <row r="467">
@@ -9741,7 +9741,7 @@
         <v>Medium</v>
       </c>
       <c r="F467">
-        <v>212</v>
+        <v>243</v>
       </c>
     </row>
     <row r="468">
@@ -9761,7 +9761,7 @@
         <v>Medium</v>
       </c>
       <c r="F468">
-        <v>133</v>
+        <v>205</v>
       </c>
     </row>
     <row r="469">
@@ -9781,7 +9781,7 @@
         <v>High</v>
       </c>
       <c r="F469">
-        <v>214</v>
+        <v>85</v>
       </c>
     </row>
     <row r="470">
@@ -9801,7 +9801,7 @@
         <v>Medium</v>
       </c>
       <c r="F470">
-        <v>148</v>
+        <v>119</v>
       </c>
     </row>
     <row r="471">
@@ -9821,7 +9821,7 @@
         <v>Medium</v>
       </c>
       <c r="F471">
-        <v>243</v>
+        <v>137</v>
       </c>
     </row>
     <row r="472">
@@ -9841,7 +9841,7 @@
         <v>Medium</v>
       </c>
       <c r="F472">
-        <v>182</v>
+        <v>253</v>
       </c>
     </row>
     <row r="473">
@@ -9861,7 +9861,7 @@
         <v>High</v>
       </c>
       <c r="F473">
-        <v>222</v>
+        <v>89</v>
       </c>
     </row>
     <row r="474">
@@ -9881,7 +9881,7 @@
         <v>Medium</v>
       </c>
       <c r="F474">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
     <row r="475">
@@ -9901,7 +9901,7 @@
         <v>Medium</v>
       </c>
       <c r="F475">
-        <v>151</v>
+        <v>277</v>
       </c>
     </row>
     <row r="476">
@@ -9921,7 +9921,7 @@
         <v>Medium</v>
       </c>
       <c r="F476">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="477">
@@ -9941,7 +9941,7 @@
         <v>High</v>
       </c>
       <c r="F477">
-        <v>161</v>
+        <v>96</v>
       </c>
     </row>
     <row r="478">
@@ -9961,7 +9961,7 @@
         <v>Medium</v>
       </c>
       <c r="F478">
-        <v>264</v>
+        <v>92</v>
       </c>
     </row>
     <row r="479">
@@ -9981,7 +9981,7 @@
         <v>Medium</v>
       </c>
       <c r="F479">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="480">
@@ -10001,7 +10001,7 @@
         <v>Medium</v>
       </c>
       <c r="F480">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="481">
@@ -10021,7 +10021,7 @@
         <v>High</v>
       </c>
       <c r="F481">
-        <v>92</v>
+        <v>254</v>
       </c>
     </row>
     <row r="482">
@@ -10041,7 +10041,7 @@
         <v>Medium</v>
       </c>
       <c r="F482">
-        <v>267</v>
+        <v>138</v>
       </c>
     </row>
     <row r="483">
@@ -10061,7 +10061,7 @@
         <v>Medium</v>
       </c>
       <c r="F483">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="484">
@@ -10081,7 +10081,7 @@
         <v>Medium</v>
       </c>
       <c r="F484">
-        <v>245</v>
+        <v>145</v>
       </c>
     </row>
     <row r="485">
@@ -10101,7 +10101,7 @@
         <v>High</v>
       </c>
       <c r="F485">
-        <v>157</v>
+        <v>247</v>
       </c>
     </row>
     <row r="486">
@@ -10121,7 +10121,7 @@
         <v>Medium</v>
       </c>
       <c r="F486">
-        <v>232</v>
+        <v>95</v>
       </c>
     </row>
     <row r="487">
@@ -10141,7 +10141,7 @@
         <v>Medium</v>
       </c>
       <c r="F487">
-        <v>112</v>
+        <v>226</v>
       </c>
     </row>
     <row r="488">
@@ -10161,7 +10161,7 @@
         <v>Medium</v>
       </c>
       <c r="F488">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="489">
@@ -10181,7 +10181,7 @@
         <v>High</v>
       </c>
       <c r="F489">
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="490">
@@ -10201,7 +10201,7 @@
         <v>Medium</v>
       </c>
       <c r="F490">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="491">
@@ -10221,7 +10221,7 @@
         <v>Medium</v>
       </c>
       <c r="F491">
-        <v>184</v>
+        <v>98</v>
       </c>
     </row>
     <row r="492">
@@ -10241,7 +10241,7 @@
         <v>Medium</v>
       </c>
       <c r="F492">
-        <v>124</v>
+        <v>204</v>
       </c>
     </row>
     <row r="493">
@@ -10261,7 +10261,7 @@
         <v>High</v>
       </c>
       <c r="F493">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="494">
@@ -10281,7 +10281,7 @@
         <v>Medium</v>
       </c>
       <c r="F494">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="495">
@@ -10301,7 +10301,7 @@
         <v>Medium</v>
       </c>
       <c r="F495">
-        <v>141</v>
+        <v>102</v>
       </c>
     </row>
     <row r="496">
@@ -10321,7 +10321,7 @@
         <v>Medium</v>
       </c>
       <c r="F496">
-        <v>174</v>
+        <v>246</v>
       </c>
     </row>
     <row r="497">
@@ -10341,7 +10341,7 @@
         <v>High</v>
       </c>
       <c r="F497">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="498">
@@ -10361,7 +10361,7 @@
         <v>Medium</v>
       </c>
       <c r="F498">
-        <v>149</v>
+        <v>183</v>
       </c>
     </row>
     <row r="499">
@@ -10381,7 +10381,7 @@
         <v>Medium</v>
       </c>
       <c r="F499">
-        <v>123</v>
+        <v>90</v>
       </c>
     </row>
     <row r="500">
@@ -10401,7 +10401,7 @@
         <v>Medium</v>
       </c>
       <c r="F500">
-        <v>248</v>
+        <v>159</v>
       </c>
     </row>
     <row r="501">
@@ -10421,7 +10421,7 @@
         <v>High</v>
       </c>
       <c r="F501">
-        <v>90</v>
+        <v>185</v>
       </c>
     </row>
     <row r="502">
@@ -10441,7 +10441,7 @@
         <v>Medium</v>
       </c>
       <c r="F502">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="503">
@@ -10461,7 +10461,7 @@
         <v>Medium</v>
       </c>
       <c r="F503">
-        <v>161</v>
+        <v>272</v>
       </c>
     </row>
     <row r="504">
@@ -10481,7 +10481,7 @@
         <v>Medium</v>
       </c>
       <c r="F504">
-        <v>240</v>
+        <v>154</v>
       </c>
     </row>
     <row r="505">
@@ -10501,7 +10501,7 @@
         <v>High</v>
       </c>
       <c r="F505">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="506">
@@ -10521,7 +10521,7 @@
         <v>Medium</v>
       </c>
       <c r="F506">
-        <v>93</v>
+        <v>166</v>
       </c>
     </row>
     <row r="507">
@@ -10541,7 +10541,7 @@
         <v>Medium</v>
       </c>
       <c r="F507">
-        <v>162</v>
+        <v>265</v>
       </c>
     </row>
     <row r="508">
@@ -10561,7 +10561,7 @@
         <v>Medium</v>
       </c>
       <c r="F508">
-        <v>248</v>
+        <v>82</v>
       </c>
     </row>
     <row r="509">
@@ -10581,7 +10581,7 @@
         <v>High</v>
       </c>
       <c r="F509">
-        <v>120</v>
+        <v>274</v>
       </c>
     </row>
     <row r="510">
@@ -10601,7 +10601,7 @@
         <v>Medium</v>
       </c>
       <c r="F510">
-        <v>82</v>
+        <v>187</v>
       </c>
     </row>
     <row r="511">
@@ -10621,7 +10621,7 @@
         <v>Medium</v>
       </c>
       <c r="F511">
-        <v>231</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -10675,7 +10675,7 @@
         <v>Medium</v>
       </c>
       <c r="F2">
-        <v>244</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
@@ -10695,7 +10695,7 @@
         <v>Medium</v>
       </c>
       <c r="F3">
-        <v>230</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4">
@@ -10715,7 +10715,7 @@
         <v>Medium</v>
       </c>
       <c r="F4">
-        <v>143</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -10735,7 +10735,7 @@
         <v>High</v>
       </c>
       <c r="F5">
-        <v>228</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -10755,7 +10755,7 @@
         <v>Medium</v>
       </c>
       <c r="F6">
-        <v>146</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7">
@@ -10775,7 +10775,7 @@
         <v>Medium</v>
       </c>
       <c r="F7">
-        <v>219</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
@@ -10795,7 +10795,7 @@
         <v>Medium</v>
       </c>
       <c r="F8">
-        <v>278</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9">
@@ -10815,7 +10815,7 @@
         <v>High</v>
       </c>
       <c r="F9">
-        <v>163</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -10835,7 +10835,7 @@
         <v>Medium</v>
       </c>
       <c r="F10">
-        <v>133</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11">
@@ -10855,7 +10855,7 @@
         <v>Medium</v>
       </c>
       <c r="F11">
-        <v>201</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -10875,7 +10875,7 @@
         <v>Medium</v>
       </c>
       <c r="F12">
-        <v>153</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -10895,7 +10895,7 @@
         <v>High</v>
       </c>
       <c r="F13">
-        <v>228</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -10915,7 +10915,7 @@
         <v>Medium</v>
       </c>
       <c r="F14">
-        <v>265</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
@@ -10935,7 +10935,7 @@
         <v>Medium</v>
       </c>
       <c r="F15">
-        <v>115</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16">
@@ -10955,7 +10955,7 @@
         <v>Medium</v>
       </c>
       <c r="F16">
-        <v>267</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -10975,7 +10975,7 @@
         <v>High</v>
       </c>
       <c r="F17">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -10995,7 +10995,7 @@
         <v>Medium</v>
       </c>
       <c r="F18">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19">
@@ -11015,7 +11015,7 @@
         <v>Medium</v>
       </c>
       <c r="F19">
-        <v>187</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20">
@@ -11035,7 +11035,7 @@
         <v>Medium</v>
       </c>
       <c r="F20">
-        <v>232</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21">
@@ -11055,7 +11055,7 @@
         <v>High</v>
       </c>
       <c r="F21">
-        <v>247</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -11075,7 +11075,7 @@
         <v>Medium</v>
       </c>
       <c r="F22">
-        <v>114</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -11095,7 +11095,7 @@
         <v>Medium</v>
       </c>
       <c r="F23">
-        <v>133</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24">
@@ -11115,7 +11115,7 @@
         <v>Medium</v>
       </c>
       <c r="F24">
-        <v>162</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -11135,7 +11135,7 @@
         <v>High</v>
       </c>
       <c r="F25">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26">
@@ -11155,7 +11155,7 @@
         <v>Medium</v>
       </c>
       <c r="F26">
-        <v>243</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27">
@@ -11175,7 +11175,7 @@
         <v>Medium</v>
       </c>
       <c r="F27">
-        <v>129</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28">
@@ -11195,7 +11195,7 @@
         <v>Medium</v>
       </c>
       <c r="F28">
-        <v>97</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29">
@@ -11215,7 +11215,7 @@
         <v>High</v>
       </c>
       <c r="F29">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30">
@@ -11235,7 +11235,7 @@
         <v>Medium</v>
       </c>
       <c r="F30">
-        <v>243</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31">
@@ -11255,7 +11255,7 @@
         <v>Medium</v>
       </c>
       <c r="F31">
-        <v>87</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32">
@@ -11275,7 +11275,7 @@
         <v>Medium</v>
       </c>
       <c r="F32">
-        <v>106</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33">
@@ -11295,7 +11295,7 @@
         <v>High</v>
       </c>
       <c r="F33">
-        <v>263</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34">
@@ -11315,7 +11315,7 @@
         <v>Medium</v>
       </c>
       <c r="F34">
-        <v>198</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
@@ -11335,7 +11335,7 @@
         <v>Medium</v>
       </c>
       <c r="F35">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36">
@@ -11355,7 +11355,7 @@
         <v>Medium</v>
       </c>
       <c r="F36">
-        <v>138</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
@@ -11375,7 +11375,7 @@
         <v>High</v>
       </c>
       <c r="F37">
-        <v>98</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38">
@@ -11395,7 +11395,7 @@
         <v>Medium</v>
       </c>
       <c r="F38">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39">
@@ -11415,7 +11415,7 @@
         <v>Medium</v>
       </c>
       <c r="F39">
-        <v>232</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40">
@@ -11435,7 +11435,7 @@
         <v>Medium</v>
       </c>
       <c r="F40">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41">
@@ -11455,7 +11455,7 @@
         <v>High</v>
       </c>
       <c r="F41">
-        <v>256</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42">
@@ -11475,7 +11475,7 @@
         <v>Medium</v>
       </c>
       <c r="F42">
-        <v>220</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43">
@@ -11495,7 +11495,7 @@
         <v>Medium</v>
       </c>
       <c r="F43">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44">
@@ -11515,7 +11515,7 @@
         <v>Medium</v>
       </c>
       <c r="F44">
-        <v>206</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
@@ -11535,7 +11535,7 @@
         <v>High</v>
       </c>
       <c r="F45">
-        <v>108</v>
+        <v>146</v>
       </c>
     </row>
     <row r="46">
@@ -11555,7 +11555,7 @@
         <v>Medium</v>
       </c>
       <c r="F46">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47">
@@ -11575,7 +11575,7 @@
         <v>Medium</v>
       </c>
       <c r="F47">
-        <v>185</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48">
@@ -11595,7 +11595,7 @@
         <v>Medium</v>
       </c>
       <c r="F48">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49">
@@ -11615,7 +11615,7 @@
         <v>High</v>
       </c>
       <c r="F49">
-        <v>211</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50">
@@ -11635,7 +11635,7 @@
         <v>Medium</v>
       </c>
       <c r="F50">
-        <v>92</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51">
@@ -11655,7 +11655,7 @@
         <v>Medium</v>
       </c>
       <c r="F51">
-        <v>197</v>
+        <v>164</v>
       </c>
     </row>
     <row r="52">
@@ -11675,7 +11675,7 @@
         <v>Medium</v>
       </c>
       <c r="F52">
-        <v>253</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53">
@@ -11695,7 +11695,7 @@
         <v>High</v>
       </c>
       <c r="F53">
-        <v>103</v>
+        <v>163</v>
       </c>
     </row>
     <row r="54">
@@ -11715,7 +11715,7 @@
         <v>Medium</v>
       </c>
       <c r="F54">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55">
@@ -11735,7 +11735,7 @@
         <v>Medium</v>
       </c>
       <c r="F55">
-        <v>257</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56">
@@ -11755,7 +11755,7 @@
         <v>Medium</v>
       </c>
       <c r="F56">
-        <v>262</v>
+        <v>133</v>
       </c>
     </row>
     <row r="57">
@@ -11775,7 +11775,7 @@
         <v>High</v>
       </c>
       <c r="F57">
-        <v>242</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58">
@@ -11795,7 +11795,7 @@
         <v>Medium</v>
       </c>
       <c r="F58">
-        <v>212</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59">
@@ -11815,7 +11815,7 @@
         <v>Medium</v>
       </c>
       <c r="F59">
-        <v>185</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60">
@@ -11835,7 +11835,7 @@
         <v>Medium</v>
       </c>
       <c r="F60">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61">
@@ -11855,7 +11855,7 @@
         <v>High</v>
       </c>
       <c r="F61">
-        <v>258</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62">
@@ -11875,7 +11875,7 @@
         <v>Medium</v>
       </c>
       <c r="F62">
-        <v>239</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63">
@@ -11895,7 +11895,7 @@
         <v>Medium</v>
       </c>
       <c r="F63">
-        <v>109</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64">
@@ -11915,7 +11915,7 @@
         <v>Medium</v>
       </c>
       <c r="F64">
-        <v>143</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65">
@@ -11935,7 +11935,7 @@
         <v>High</v>
       </c>
       <c r="F65">
-        <v>113</v>
+        <v>271</v>
       </c>
     </row>
     <row r="66">
@@ -11955,7 +11955,7 @@
         <v>Medium</v>
       </c>
       <c r="F66">
-        <v>126</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67">
@@ -11975,7 +11975,7 @@
         <v>Medium</v>
       </c>
       <c r="F67">
-        <v>125</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68">
@@ -11995,7 +11995,7 @@
         <v>Medium</v>
       </c>
       <c r="F68">
-        <v>204</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69">
@@ -12015,7 +12015,7 @@
         <v>High</v>
       </c>
       <c r="F69">
-        <v>142</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70">
@@ -12035,7 +12035,7 @@
         <v>Medium</v>
       </c>
       <c r="F70">
-        <v>193</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71">
@@ -12055,7 +12055,7 @@
         <v>Medium</v>
       </c>
       <c r="F71">
-        <v>168</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72">
@@ -12075,7 +12075,7 @@
         <v>Medium</v>
       </c>
       <c r="F72">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="73">
@@ -12095,7 +12095,7 @@
         <v>Medium</v>
       </c>
       <c r="F73">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74">
@@ -12115,7 +12115,7 @@
         <v>Medium</v>
       </c>
       <c r="F74">
-        <v>148</v>
+        <v>109</v>
       </c>
     </row>
     <row r="75">
@@ -12135,7 +12135,7 @@
         <v>High</v>
       </c>
       <c r="F75">
-        <v>175</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76">
@@ -12155,7 +12155,7 @@
         <v>Medium</v>
       </c>
       <c r="F76">
-        <v>80</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77">
@@ -12175,7 +12175,7 @@
         <v>Medium</v>
       </c>
       <c r="F77">
-        <v>270</v>
+        <v>130</v>
       </c>
     </row>
     <row r="78">
@@ -12195,7 +12195,7 @@
         <v>Medium</v>
       </c>
       <c r="F78">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="79">
@@ -12215,7 +12215,7 @@
         <v>High</v>
       </c>
       <c r="F79">
-        <v>110</v>
+        <v>215</v>
       </c>
     </row>
     <row r="80">
@@ -12235,7 +12235,7 @@
         <v>Medium</v>
       </c>
       <c r="F80">
-        <v>255</v>
+        <v>137</v>
       </c>
     </row>
     <row r="81">
@@ -12255,7 +12255,7 @@
         <v>Medium</v>
       </c>
       <c r="F81">
-        <v>88</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82">
@@ -12275,7 +12275,7 @@
         <v>Medium</v>
       </c>
       <c r="F82">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
@@ -12295,7 +12295,7 @@
         <v>High</v>
       </c>
       <c r="F83">
-        <v>204</v>
+        <v>99</v>
       </c>
     </row>
     <row r="84">
@@ -12315,7 +12315,7 @@
         <v>Medium</v>
       </c>
       <c r="F84">
-        <v>112</v>
+        <v>255</v>
       </c>
     </row>
     <row r="85">
@@ -12335,7 +12335,7 @@
         <v>Medium</v>
       </c>
       <c r="F85">
-        <v>216</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86">
@@ -12355,7 +12355,7 @@
         <v>Medium</v>
       </c>
       <c r="F86">
-        <v>245</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87">
@@ -12375,7 +12375,7 @@
         <v>High</v>
       </c>
       <c r="F87">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="88">
@@ -12395,7 +12395,7 @@
         <v>Medium</v>
       </c>
       <c r="F88">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89">
@@ -12415,7 +12415,7 @@
         <v>Medium</v>
       </c>
       <c r="F89">
-        <v>263</v>
+        <v>165</v>
       </c>
     </row>
     <row r="90">
@@ -12435,7 +12435,7 @@
         <v>Medium</v>
       </c>
       <c r="F90">
-        <v>158</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91">
@@ -12455,7 +12455,7 @@
         <v>High</v>
       </c>
       <c r="F91">
-        <v>139</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92">
@@ -12475,7 +12475,7 @@
         <v>Medium</v>
       </c>
       <c r="F92">
-        <v>133</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93">
@@ -12495,7 +12495,7 @@
         <v>Medium</v>
       </c>
       <c r="F93">
-        <v>247</v>
+        <v>154</v>
       </c>
     </row>
     <row r="94">
@@ -12515,7 +12515,7 @@
         <v>Medium</v>
       </c>
       <c r="F94">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95">
@@ -12535,7 +12535,7 @@
         <v>High</v>
       </c>
       <c r="F95">
-        <v>134</v>
+        <v>259</v>
       </c>
     </row>
     <row r="96">
@@ -12555,7 +12555,7 @@
         <v>Medium</v>
       </c>
       <c r="F96">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97">
@@ -12575,7 +12575,7 @@
         <v>Medium</v>
       </c>
       <c r="F97">
-        <v>139</v>
+        <v>230</v>
       </c>
     </row>
     <row r="98">
@@ -12595,7 +12595,7 @@
         <v>Medium</v>
       </c>
       <c r="F98">
-        <v>163</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99">
@@ -12615,7 +12615,7 @@
         <v>High</v>
       </c>
       <c r="F99">
-        <v>173</v>
+        <v>201</v>
       </c>
     </row>
     <row r="100">
@@ -12635,7 +12635,7 @@
         <v>Medium</v>
       </c>
       <c r="F100">
-        <v>132</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101">
@@ -12655,7 +12655,7 @@
         <v>Medium</v>
       </c>
       <c r="F101">
-        <v>159</v>
+        <v>111</v>
       </c>
     </row>
     <row r="102">
@@ -12695,7 +12695,7 @@
         <v>High</v>
       </c>
       <c r="F103">
-        <v>211</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104">
@@ -12715,7 +12715,7 @@
         <v>Medium</v>
       </c>
       <c r="F104">
-        <v>247</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105">
@@ -12735,7 +12735,7 @@
         <v>Medium</v>
       </c>
       <c r="F105">
-        <v>170</v>
+        <v>119</v>
       </c>
     </row>
     <row r="106">
@@ -12755,7 +12755,7 @@
         <v>Medium</v>
       </c>
       <c r="F106">
-        <v>261</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107">
@@ -12775,7 +12775,7 @@
         <v>High</v>
       </c>
       <c r="F107">
-        <v>237</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108">
@@ -12795,7 +12795,7 @@
         <v>Medium</v>
       </c>
       <c r="F108">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109">
@@ -12815,7 +12815,7 @@
         <v>Medium</v>
       </c>
       <c r="F109">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110">
@@ -12835,7 +12835,7 @@
         <v>Medium</v>
       </c>
       <c r="F110">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="111">
@@ -12855,7 +12855,7 @@
         <v>High</v>
       </c>
       <c r="F111">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112">
@@ -12875,7 +12875,7 @@
         <v>Medium</v>
       </c>
       <c r="F112">
-        <v>247</v>
+        <v>105</v>
       </c>
     </row>
     <row r="113">
@@ -12895,7 +12895,7 @@
         <v>Medium</v>
       </c>
       <c r="F113">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="114">
@@ -12915,7 +12915,7 @@
         <v>Medium</v>
       </c>
       <c r="F114">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115">
@@ -12935,7 +12935,7 @@
         <v>High</v>
       </c>
       <c r="F115">
-        <v>248</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116">
@@ -12955,7 +12955,7 @@
         <v>Medium</v>
       </c>
       <c r="F116">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
@@ -12975,7 +12975,7 @@
         <v>Medium</v>
       </c>
       <c r="F117">
-        <v>222</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118">
@@ -12995,7 +12995,7 @@
         <v>Medium</v>
       </c>
       <c r="F118">
-        <v>163</v>
+        <v>211</v>
       </c>
     </row>
     <row r="119">
@@ -13015,7 +13015,7 @@
         <v>High</v>
       </c>
       <c r="F119">
-        <v>107</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120">
@@ -13035,7 +13035,7 @@
         <v>Medium</v>
       </c>
       <c r="F120">
-        <v>275</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121">
@@ -13055,7 +13055,7 @@
         <v>Medium</v>
       </c>
       <c r="F121">
-        <v>171</v>
+        <v>241</v>
       </c>
     </row>
     <row r="122">
@@ -13075,7 +13075,7 @@
         <v>Medium</v>
       </c>
       <c r="F122">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123">
@@ -13095,7 +13095,7 @@
         <v>High</v>
       </c>
       <c r="F123">
-        <v>184</v>
+        <v>119</v>
       </c>
     </row>
     <row r="124">
@@ -13115,7 +13115,7 @@
         <v>Medium</v>
       </c>
       <c r="F124">
-        <v>127</v>
+        <v>196</v>
       </c>
     </row>
     <row r="125">
@@ -13135,7 +13135,7 @@
         <v>Medium</v>
       </c>
       <c r="F125">
-        <v>248</v>
+        <v>170</v>
       </c>
     </row>
     <row r="126">
@@ -13155,7 +13155,7 @@
         <v>Medium</v>
       </c>
       <c r="F126">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="127">
@@ -13175,7 +13175,7 @@
         <v>High</v>
       </c>
       <c r="F127">
-        <v>136</v>
+        <v>87</v>
       </c>
     </row>
     <row r="128">
@@ -13195,7 +13195,7 @@
         <v>Medium</v>
       </c>
       <c r="F128">
-        <v>193</v>
+        <v>235</v>
       </c>
     </row>
     <row r="129">
@@ -13215,7 +13215,7 @@
         <v>Medium</v>
       </c>
       <c r="F129">
-        <v>217</v>
+        <v>131</v>
       </c>
     </row>
     <row r="130">
@@ -13235,7 +13235,7 @@
         <v>Medium</v>
       </c>
       <c r="F130">
-        <v>94</v>
+        <v>173</v>
       </c>
     </row>
     <row r="131">
@@ -13255,7 +13255,7 @@
         <v>High</v>
       </c>
       <c r="F131">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="132">
@@ -13275,7 +13275,7 @@
         <v>Medium</v>
       </c>
       <c r="F132">
-        <v>278</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133">
@@ -13295,7 +13295,7 @@
         <v>Medium</v>
       </c>
       <c r="F133">
-        <v>209</v>
+        <v>151</v>
       </c>
     </row>
     <row r="134">
@@ -13315,7 +13315,7 @@
         <v>Medium</v>
       </c>
       <c r="F134">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="135">
@@ -13335,7 +13335,7 @@
         <v>High</v>
       </c>
       <c r="F135">
-        <v>154</v>
+        <v>172</v>
       </c>
     </row>
     <row r="136">
@@ -13355,7 +13355,7 @@
         <v>Medium</v>
       </c>
       <c r="F136">
-        <v>153</v>
+        <v>184</v>
       </c>
     </row>
     <row r="137">
@@ -13375,7 +13375,7 @@
         <v>Medium</v>
       </c>
       <c r="F137">
-        <v>206</v>
+        <v>159</v>
       </c>
     </row>
     <row r="138">
@@ -13395,7 +13395,7 @@
         <v>Medium</v>
       </c>
       <c r="F138">
-        <v>120</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139">
@@ -13415,7 +13415,7 @@
         <v>High</v>
       </c>
       <c r="F139">
-        <v>193</v>
+        <v>115</v>
       </c>
     </row>
     <row r="140">
@@ -13435,7 +13435,7 @@
         <v>Medium</v>
       </c>
       <c r="F140">
-        <v>203</v>
+        <v>235</v>
       </c>
     </row>
     <row r="141">
@@ -13455,7 +13455,7 @@
         <v>Medium</v>
       </c>
       <c r="F141">
-        <v>170</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -13475,7 +13475,7 @@
         <v>Medium</v>
       </c>
       <c r="F142">
-        <v>93</v>
+        <v>216</v>
       </c>
     </row>
     <row r="143">
@@ -13495,7 +13495,7 @@
         <v>Medium</v>
       </c>
       <c r="F143">
-        <v>257</v>
+        <v>200</v>
       </c>
     </row>
     <row r="144">
@@ -13515,7 +13515,7 @@
         <v>Medium</v>
       </c>
       <c r="F144">
-        <v>189</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145">
@@ -13535,7 +13535,7 @@
         <v>High</v>
       </c>
       <c r="F145">
-        <v>102</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
@@ -13555,7 +13555,7 @@
         <v>Medium</v>
       </c>
       <c r="F146">
-        <v>92</v>
+        <v>220</v>
       </c>
     </row>
     <row r="147">
@@ -13575,7 +13575,7 @@
         <v>Medium</v>
       </c>
       <c r="F147">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="148">
@@ -13595,7 +13595,7 @@
         <v>Medium</v>
       </c>
       <c r="F148">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="149">
@@ -13615,7 +13615,7 @@
         <v>High</v>
       </c>
       <c r="F149">
-        <v>178</v>
+        <v>119</v>
       </c>
     </row>
     <row r="150">
@@ -13635,7 +13635,7 @@
         <v>Medium</v>
       </c>
       <c r="F150">
-        <v>170</v>
+        <v>106</v>
       </c>
     </row>
     <row r="151">
@@ -13655,7 +13655,7 @@
         <v>Medium</v>
       </c>
       <c r="F151">
-        <v>225</v>
+        <v>153</v>
       </c>
     </row>
     <row r="152">
@@ -13675,7 +13675,7 @@
         <v>Medium</v>
       </c>
       <c r="F152">
-        <v>197</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153">
@@ -13695,7 +13695,7 @@
         <v>High</v>
       </c>
       <c r="F153">
-        <v>96</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154">
@@ -13715,7 +13715,7 @@
         <v>Medium</v>
       </c>
       <c r="F154">
-        <v>267</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155">
@@ -13735,7 +13735,7 @@
         <v>Medium</v>
       </c>
       <c r="F155">
-        <v>169</v>
+        <v>95</v>
       </c>
     </row>
     <row r="156">
@@ -13755,7 +13755,7 @@
         <v>Medium</v>
       </c>
       <c r="F156">
-        <v>256</v>
+        <v>84</v>
       </c>
     </row>
     <row r="157">
@@ -13775,7 +13775,7 @@
         <v>High</v>
       </c>
       <c r="F157">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="158">
@@ -13795,7 +13795,7 @@
         <v>Medium</v>
       </c>
       <c r="F158">
-        <v>269</v>
+        <v>148</v>
       </c>
     </row>
     <row r="159">
@@ -13815,7 +13815,7 @@
         <v>Medium</v>
       </c>
       <c r="F159">
-        <v>183</v>
+        <v>172</v>
       </c>
     </row>
     <row r="160">
@@ -13835,7 +13835,7 @@
         <v>Medium</v>
       </c>
       <c r="F160">
-        <v>174</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161">
@@ -13855,7 +13855,7 @@
         <v>High</v>
       </c>
       <c r="F161">
-        <v>265</v>
+        <v>197</v>
       </c>
     </row>
     <row r="162">
@@ -13875,7 +13875,7 @@
         <v>Medium</v>
       </c>
       <c r="F162">
-        <v>273</v>
+        <v>164</v>
       </c>
     </row>
     <row r="163">
@@ -13895,7 +13895,7 @@
         <v>Medium</v>
       </c>
       <c r="F163">
-        <v>234</v>
+        <v>102</v>
       </c>
     </row>
     <row r="164">
@@ -13915,7 +13915,7 @@
         <v>Medium</v>
       </c>
       <c r="F164">
-        <v>147</v>
+        <v>241</v>
       </c>
     </row>
     <row r="165">
@@ -13935,7 +13935,7 @@
         <v>High</v>
       </c>
       <c r="F165">
-        <v>111</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166">
@@ -13955,7 +13955,7 @@
         <v>Medium</v>
       </c>
       <c r="F166">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="167">
@@ -13975,7 +13975,7 @@
         <v>Medium</v>
       </c>
       <c r="F167">
-        <v>112</v>
+        <v>189</v>
       </c>
     </row>
     <row r="168">
@@ -13995,7 +13995,7 @@
         <v>Medium</v>
       </c>
       <c r="F168">
-        <v>216</v>
+        <v>263</v>
       </c>
     </row>
     <row r="169">
@@ -14015,7 +14015,7 @@
         <v>High</v>
       </c>
       <c r="F169">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="170">
@@ -14035,7 +14035,7 @@
         <v>Medium</v>
       </c>
       <c r="F170">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171">
@@ -14055,7 +14055,7 @@
         <v>Medium</v>
       </c>
       <c r="F171">
-        <v>117</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172">
@@ -14075,7 +14075,7 @@
         <v>Medium</v>
       </c>
       <c r="F172">
-        <v>275</v>
+        <v>135</v>
       </c>
     </row>
     <row r="173">
@@ -14095,7 +14095,7 @@
         <v>High</v>
       </c>
       <c r="F173">
-        <v>240</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174">
@@ -14115,7 +14115,7 @@
         <v>Medium</v>
       </c>
       <c r="F174">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="175">
@@ -14135,7 +14135,7 @@
         <v>Medium</v>
       </c>
       <c r="F175">
-        <v>150</v>
+        <v>271</v>
       </c>
     </row>
     <row r="176">
@@ -14155,7 +14155,7 @@
         <v>Medium</v>
       </c>
       <c r="F176">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177">
@@ -14175,7 +14175,7 @@
         <v>High</v>
       </c>
       <c r="F177">
-        <v>271</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178">
@@ -14195,7 +14195,7 @@
         <v>Medium</v>
       </c>
       <c r="F178">
-        <v>196</v>
+        <v>134</v>
       </c>
     </row>
     <row r="179">
@@ -14215,7 +14215,7 @@
         <v>Medium</v>
       </c>
       <c r="F179">
-        <v>243</v>
+        <v>279</v>
       </c>
     </row>
     <row r="180">
@@ -14235,7 +14235,7 @@
         <v>Medium</v>
       </c>
       <c r="F180">
-        <v>185</v>
+        <v>138</v>
       </c>
     </row>
     <row r="181">
@@ -14255,7 +14255,7 @@
         <v>High</v>
       </c>
       <c r="F181">
-        <v>115</v>
+        <v>218</v>
       </c>
     </row>
     <row r="182">
@@ -14275,7 +14275,7 @@
         <v>Medium</v>
       </c>
       <c r="F182">
-        <v>96</v>
+        <v>161</v>
       </c>
     </row>
     <row r="183">
@@ -14295,7 +14295,7 @@
         <v>Medium</v>
       </c>
       <c r="F183">
-        <v>140</v>
+        <v>251</v>
       </c>
     </row>
     <row r="184">
@@ -14315,7 +14315,7 @@
         <v>Medium</v>
       </c>
       <c r="F184">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185">
@@ -14335,7 +14335,7 @@
         <v>High</v>
       </c>
       <c r="F185">
-        <v>265</v>
+        <v>241</v>
       </c>
     </row>
     <row r="186">
@@ -14355,7 +14355,7 @@
         <v>Medium</v>
       </c>
       <c r="F186">
-        <v>137</v>
+        <v>83</v>
       </c>
     </row>
     <row r="187">
@@ -14375,7 +14375,7 @@
         <v>Medium</v>
       </c>
       <c r="F187">
-        <v>139</v>
+        <v>197</v>
       </c>
     </row>
     <row r="188">
@@ -14395,7 +14395,7 @@
         <v>Medium</v>
       </c>
       <c r="F188">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="189">
@@ -14415,7 +14415,7 @@
         <v>High</v>
       </c>
       <c r="F189">
-        <v>254</v>
+        <v>231</v>
       </c>
     </row>
     <row r="190">
@@ -14435,7 +14435,7 @@
         <v>Medium</v>
       </c>
       <c r="F190">
-        <v>219</v>
+        <v>268</v>
       </c>
     </row>
     <row r="191">
@@ -14455,7 +14455,7 @@
         <v>Medium</v>
       </c>
       <c r="F191">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="192">
@@ -14475,7 +14475,7 @@
         <v>Medium</v>
       </c>
       <c r="F192">
-        <v>120</v>
+        <v>181</v>
       </c>
     </row>
     <row r="193">
@@ -14495,7 +14495,7 @@
         <v>High</v>
       </c>
       <c r="F193">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="194">
@@ -14515,7 +14515,7 @@
         <v>Medium</v>
       </c>
       <c r="F194">
-        <v>103</v>
+        <v>157</v>
       </c>
     </row>
     <row r="195">
@@ -14535,7 +14535,7 @@
         <v>Medium</v>
       </c>
       <c r="F195">
-        <v>198</v>
+        <v>139</v>
       </c>
     </row>
     <row r="196">
@@ -14555,7 +14555,7 @@
         <v>Medium</v>
       </c>
       <c r="F196">
-        <v>247</v>
+        <v>84</v>
       </c>
     </row>
     <row r="197">
@@ -14575,7 +14575,7 @@
         <v>High</v>
       </c>
       <c r="F197">
-        <v>156</v>
+        <v>134</v>
       </c>
     </row>
     <row r="198">
@@ -14595,7 +14595,7 @@
         <v>Medium</v>
       </c>
       <c r="F198">
-        <v>212</v>
+        <v>236</v>
       </c>
     </row>
     <row r="199">
@@ -14615,7 +14615,7 @@
         <v>Medium</v>
       </c>
       <c r="F199">
-        <v>267</v>
+        <v>201</v>
       </c>
     </row>
     <row r="200">
@@ -14635,7 +14635,7 @@
         <v>Medium</v>
       </c>
       <c r="F200">
-        <v>160</v>
+        <v>271</v>
       </c>
     </row>
     <row r="201">
@@ -14655,7 +14655,7 @@
         <v>High</v>
       </c>
       <c r="F201">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="202">
@@ -14675,7 +14675,7 @@
         <v>Medium</v>
       </c>
       <c r="F202">
-        <v>229</v>
+        <v>137</v>
       </c>
     </row>
     <row r="203">
@@ -14695,7 +14695,7 @@
         <v>Medium</v>
       </c>
       <c r="F203">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="204">
@@ -14715,7 +14715,7 @@
         <v>Medium</v>
       </c>
       <c r="F204">
-        <v>205</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205">
@@ -14735,7 +14735,7 @@
         <v>High</v>
       </c>
       <c r="F205">
-        <v>178</v>
+        <v>232</v>
       </c>
     </row>
     <row r="206">
@@ -14755,7 +14755,7 @@
         <v>Medium</v>
       </c>
       <c r="F206">
-        <v>274</v>
+        <v>261</v>
       </c>
     </row>
     <row r="207">
@@ -14775,7 +14775,7 @@
         <v>Medium</v>
       </c>
       <c r="F207">
-        <v>231</v>
+        <v>102</v>
       </c>
     </row>
     <row r="208">
@@ -14795,7 +14795,7 @@
         <v>Medium</v>
       </c>
       <c r="F208">
-        <v>155</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209">
@@ -14815,7 +14815,7 @@
         <v>High</v>
       </c>
       <c r="F209">
-        <v>94</v>
+        <v>114</v>
       </c>
     </row>
     <row r="210">
@@ -14835,7 +14835,7 @@
         <v>Medium</v>
       </c>
       <c r="F210">
-        <v>163</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211">
@@ -14855,7 +14855,7 @@
         <v>Medium</v>
       </c>
       <c r="F211">
-        <v>240</v>
+        <v>87</v>
       </c>
     </row>
     <row r="212">
@@ -14875,7 +14875,7 @@
         <v>Medium</v>
       </c>
       <c r="F212">
-        <v>194</v>
+        <v>171</v>
       </c>
     </row>
     <row r="213">
@@ -14895,7 +14895,7 @@
         <v>High</v>
       </c>
       <c r="F213">
-        <v>82</v>
+        <v>141</v>
       </c>
     </row>
     <row r="214">
@@ -14915,7 +14915,7 @@
         <v>Medium</v>
       </c>
       <c r="F214">
-        <v>202</v>
+        <v>94</v>
       </c>
     </row>
     <row r="215">
@@ -14935,7 +14935,7 @@
         <v>Medium</v>
       </c>
       <c r="F215">
-        <v>232</v>
+        <v>112</v>
       </c>
     </row>
     <row r="216">
@@ -14955,7 +14955,7 @@
         <v>Medium</v>
       </c>
       <c r="F216">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="217">
@@ -14975,7 +14975,7 @@
         <v>High</v>
       </c>
       <c r="F217">
-        <v>89</v>
+        <v>162</v>
       </c>
     </row>
     <row r="218">
@@ -14995,7 +14995,7 @@
         <v>Medium</v>
       </c>
       <c r="F218">
-        <v>175</v>
+        <v>85</v>
       </c>
     </row>
     <row r="219">
@@ -15015,7 +15015,7 @@
         <v>Medium</v>
       </c>
       <c r="F219">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="220">
@@ -15035,7 +15035,7 @@
         <v>Medium</v>
       </c>
       <c r="F220">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="221">
@@ -15075,7 +15075,7 @@
         <v>Medium</v>
       </c>
       <c r="F222">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="223">
@@ -15095,7 +15095,7 @@
         <v>Medium</v>
       </c>
       <c r="F223">
-        <v>154</v>
+        <v>209</v>
       </c>
     </row>
     <row r="224">
@@ -15115,7 +15115,7 @@
         <v>Medium</v>
       </c>
       <c r="F224">
-        <v>218</v>
+        <v>139</v>
       </c>
     </row>
     <row r="225">
@@ -15135,7 +15135,7 @@
         <v>High</v>
       </c>
       <c r="F225">
-        <v>100</v>
+        <v>212</v>
       </c>
     </row>
     <row r="226">
@@ -15155,7 +15155,7 @@
         <v>Medium</v>
       </c>
       <c r="F226">
-        <v>236</v>
+        <v>195</v>
       </c>
     </row>
     <row r="227">
@@ -15175,7 +15175,7 @@
         <v>Medium</v>
       </c>
       <c r="F227">
-        <v>164</v>
+        <v>86</v>
       </c>
     </row>
     <row r="228">
@@ -15195,7 +15195,7 @@
         <v>Medium</v>
       </c>
       <c r="F228">
-        <v>235</v>
+        <v>176</v>
       </c>
     </row>
     <row r="229">
@@ -15215,7 +15215,7 @@
         <v>High</v>
       </c>
       <c r="F229">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="230">
@@ -15235,7 +15235,7 @@
         <v>Medium</v>
       </c>
       <c r="F230">
-        <v>122</v>
+        <v>177</v>
       </c>
     </row>
     <row r="231">
@@ -15255,7 +15255,7 @@
         <v>Medium</v>
       </c>
       <c r="F231">
-        <v>109</v>
+        <v>169</v>
       </c>
     </row>
     <row r="232">
@@ -15275,7 +15275,7 @@
         <v>Medium</v>
       </c>
       <c r="F232">
-        <v>211</v>
+        <v>166</v>
       </c>
     </row>
     <row r="233">
@@ -15295,7 +15295,7 @@
         <v>High</v>
       </c>
       <c r="F233">
-        <v>241</v>
+        <v>275</v>
       </c>
     </row>
     <row r="234">
@@ -15315,7 +15315,7 @@
         <v>Medium</v>
       </c>
       <c r="F234">
-        <v>177</v>
+        <v>82</v>
       </c>
     </row>
     <row r="235">
@@ -15335,7 +15335,7 @@
         <v>Medium</v>
       </c>
       <c r="F235">
-        <v>219</v>
+        <v>248</v>
       </c>
     </row>
     <row r="236">
@@ -15355,7 +15355,7 @@
         <v>Medium</v>
       </c>
       <c r="F236">
-        <v>229</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237">
@@ -15375,7 +15375,7 @@
         <v>High</v>
       </c>
       <c r="F237">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="238">
@@ -15395,7 +15395,7 @@
         <v>Medium</v>
       </c>
       <c r="F238">
-        <v>207</v>
+        <v>120</v>
       </c>
     </row>
     <row r="239">
@@ -15415,7 +15415,7 @@
         <v>Medium</v>
       </c>
       <c r="F239">
-        <v>142</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240">
@@ -15435,7 +15435,7 @@
         <v>Medium</v>
       </c>
       <c r="F240">
-        <v>279</v>
+        <v>232</v>
       </c>
     </row>
     <row r="241">
@@ -15455,7 +15455,7 @@
         <v>High</v>
       </c>
       <c r="F241">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="242">
@@ -15475,7 +15475,7 @@
         <v>Medium</v>
       </c>
       <c r="F242">
-        <v>80</v>
+        <v>186</v>
       </c>
     </row>
     <row r="243">
@@ -15495,7 +15495,7 @@
         <v>Medium</v>
       </c>
       <c r="F243">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="244">
@@ -15515,7 +15515,7 @@
         <v>Medium</v>
       </c>
       <c r="F244">
-        <v>210</v>
+        <v>221</v>
       </c>
     </row>
     <row r="245">
@@ -15535,7 +15535,7 @@
         <v>High</v>
       </c>
       <c r="F245">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="246">
@@ -15555,7 +15555,7 @@
         <v>Medium</v>
       </c>
       <c r="F246">
-        <v>273</v>
+        <v>213</v>
       </c>
     </row>
     <row r="247">
@@ -15575,7 +15575,7 @@
         <v>Medium</v>
       </c>
       <c r="F247">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248">
@@ -15595,7 +15595,7 @@
         <v>Medium</v>
       </c>
       <c r="F248">
-        <v>120</v>
+        <v>83</v>
       </c>
     </row>
     <row r="249">
@@ -15615,7 +15615,7 @@
         <v>High</v>
       </c>
       <c r="F249">
-        <v>101</v>
+        <v>204</v>
       </c>
     </row>
     <row r="250">
@@ -15635,7 +15635,7 @@
         <v>Medium</v>
       </c>
       <c r="F250">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="251">
@@ -15655,7 +15655,7 @@
         <v>Medium</v>
       </c>
       <c r="F251">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="252">
@@ -15675,7 +15675,7 @@
         <v>Medium</v>
       </c>
       <c r="F252">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="253">
@@ -15695,7 +15695,7 @@
         <v>High</v>
       </c>
       <c r="F253">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="254">
@@ -15715,7 +15715,7 @@
         <v>Medium</v>
       </c>
       <c r="F254">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="255">
@@ -15735,7 +15735,7 @@
         <v>Medium</v>
       </c>
       <c r="F255">
-        <v>198</v>
+        <v>266</v>
       </c>
     </row>
     <row r="256">
@@ -15755,7 +15755,7 @@
         <v>Medium</v>
       </c>
       <c r="F256">
-        <v>206</v>
+        <v>86</v>
       </c>
     </row>
     <row r="257">
@@ -15775,7 +15775,7 @@
         <v>High</v>
       </c>
       <c r="F257">
-        <v>216</v>
+        <v>270</v>
       </c>
     </row>
     <row r="258">
@@ -15795,7 +15795,7 @@
         <v>Medium</v>
       </c>
       <c r="F258">
-        <v>275</v>
+        <v>225</v>
       </c>
     </row>
     <row r="259">
@@ -15815,7 +15815,7 @@
         <v>Medium</v>
       </c>
       <c r="F259">
-        <v>123</v>
+        <v>184</v>
       </c>
     </row>
     <row r="260">
@@ -15835,7 +15835,7 @@
         <v>Medium</v>
       </c>
       <c r="F260">
-        <v>262</v>
+        <v>180</v>
       </c>
     </row>
     <row r="261">
@@ -15855,7 +15855,7 @@
         <v>High</v>
       </c>
       <c r="F261">
-        <v>223</v>
+        <v>272</v>
       </c>
     </row>
     <row r="262">
@@ -15875,7 +15875,7 @@
         <v>Medium</v>
       </c>
       <c r="F262">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="263">
@@ -15895,7 +15895,7 @@
         <v>Medium</v>
       </c>
       <c r="F263">
-        <v>189</v>
+        <v>92</v>
       </c>
     </row>
     <row r="264">
@@ -15915,7 +15915,7 @@
         <v>Medium</v>
       </c>
       <c r="F264">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
     <row r="265">
@@ -15935,7 +15935,7 @@
         <v>High</v>
       </c>
       <c r="F265">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="266">
@@ -15955,7 +15955,7 @@
         <v>Medium</v>
       </c>
       <c r="F266">
-        <v>269</v>
+        <v>246</v>
       </c>
     </row>
     <row r="267">
@@ -15975,7 +15975,7 @@
         <v>Medium</v>
       </c>
       <c r="F267">
-        <v>190</v>
+        <v>165</v>
       </c>
     </row>
     <row r="268">
@@ -15995,7 +15995,7 @@
         <v>Medium</v>
       </c>
       <c r="F268">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="269">
@@ -16015,7 +16015,7 @@
         <v>High</v>
       </c>
       <c r="F269">
-        <v>210</v>
+        <v>161</v>
       </c>
     </row>
     <row r="270">
@@ -16035,7 +16035,7 @@
         <v>Medium</v>
       </c>
       <c r="F270">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="271">
@@ -16055,7 +16055,7 @@
         <v>Medium</v>
       </c>
       <c r="F271">
-        <v>238</v>
+        <v>171</v>
       </c>
     </row>
     <row r="272">
@@ -16075,7 +16075,7 @@
         <v>Medium</v>
       </c>
       <c r="F272">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="273">
@@ -16095,7 +16095,7 @@
         <v>High</v>
       </c>
       <c r="F273">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="274">
@@ -16115,7 +16115,7 @@
         <v>Medium</v>
       </c>
       <c r="F274">
-        <v>273</v>
+        <v>223</v>
       </c>
     </row>
     <row r="275">
@@ -16135,7 +16135,7 @@
         <v>Medium</v>
       </c>
       <c r="F275">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="276">
@@ -16155,7 +16155,7 @@
         <v>Medium</v>
       </c>
       <c r="F276">
-        <v>135</v>
+        <v>189</v>
       </c>
     </row>
     <row r="277">
@@ -16175,7 +16175,7 @@
         <v>High</v>
       </c>
       <c r="F277">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="278">
@@ -16195,7 +16195,7 @@
         <v>Medium</v>
       </c>
       <c r="F278">
-        <v>233</v>
+        <v>83</v>
       </c>
     </row>
     <row r="279">
@@ -16215,7 +16215,7 @@
         <v>Medium</v>
       </c>
       <c r="F279">
-        <v>210</v>
+        <v>116</v>
       </c>
     </row>
     <row r="280">
@@ -16235,7 +16235,7 @@
         <v>Medium</v>
       </c>
       <c r="F280">
-        <v>217</v>
+        <v>88</v>
       </c>
     </row>
     <row r="281">
@@ -16255,7 +16255,7 @@
         <v>High</v>
       </c>
       <c r="F281">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="282">
@@ -16275,7 +16275,7 @@
         <v>Medium</v>
       </c>
       <c r="F282">
-        <v>155</v>
+        <v>219</v>
       </c>
     </row>
     <row r="283">
@@ -16295,7 +16295,7 @@
         <v>Medium</v>
       </c>
       <c r="F283">
-        <v>270</v>
+        <v>202</v>
       </c>
     </row>
     <row r="284">
@@ -16315,7 +16315,7 @@
         <v>Medium</v>
       </c>
       <c r="F284">
-        <v>206</v>
+        <v>171</v>
       </c>
     </row>
     <row r="285">
@@ -16335,7 +16335,7 @@
         <v>High</v>
       </c>
       <c r="F285">
-        <v>274</v>
+        <v>160</v>
       </c>
     </row>
     <row r="286">
@@ -16355,7 +16355,7 @@
         <v>Medium</v>
       </c>
       <c r="F286">
-        <v>221</v>
+        <v>127</v>
       </c>
     </row>
     <row r="287">
@@ -16375,7 +16375,7 @@
         <v>Medium</v>
       </c>
       <c r="F287">
-        <v>121</v>
+        <v>240</v>
       </c>
     </row>
     <row r="288">
@@ -16395,7 +16395,7 @@
         <v>Medium</v>
       </c>
       <c r="F288">
-        <v>237</v>
+        <v>99</v>
       </c>
     </row>
     <row r="289">
@@ -16415,7 +16415,7 @@
         <v>High</v>
       </c>
       <c r="F289">
-        <v>239</v>
+        <v>175</v>
       </c>
     </row>
     <row r="290">
@@ -16435,7 +16435,7 @@
         <v>Medium</v>
       </c>
       <c r="F290">
-        <v>248</v>
+        <v>195</v>
       </c>
     </row>
     <row r="291">
@@ -16455,7 +16455,7 @@
         <v>Medium</v>
       </c>
       <c r="F291">
-        <v>140</v>
+        <v>184</v>
       </c>
     </row>
     <row r="292">
@@ -16475,7 +16475,7 @@
         <v>Medium</v>
       </c>
       <c r="F292">
-        <v>149</v>
+        <v>89</v>
       </c>
     </row>
     <row r="293">
@@ -16495,7 +16495,7 @@
         <v>High</v>
       </c>
       <c r="F293">
-        <v>121</v>
+        <v>276</v>
       </c>
     </row>
     <row r="294">
@@ -16515,7 +16515,7 @@
         <v>Medium</v>
       </c>
       <c r="F294">
-        <v>153</v>
+        <v>111</v>
       </c>
     </row>
     <row r="295">
@@ -16535,7 +16535,7 @@
         <v>Medium</v>
       </c>
       <c r="F295">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="296">
@@ -16555,7 +16555,7 @@
         <v>Medium</v>
       </c>
       <c r="F296">
-        <v>136</v>
+        <v>262</v>
       </c>
     </row>
     <row r="297">
@@ -16575,7 +16575,7 @@
         <v>High</v>
       </c>
       <c r="F297">
-        <v>273</v>
+        <v>156</v>
       </c>
     </row>
     <row r="298">
@@ -16595,7 +16595,7 @@
         <v>Medium</v>
       </c>
       <c r="F298">
-        <v>113</v>
+        <v>241</v>
       </c>
     </row>
     <row r="299">
@@ -16615,7 +16615,7 @@
         <v>Medium</v>
       </c>
       <c r="F299">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="300">
@@ -16635,7 +16635,7 @@
         <v>Medium</v>
       </c>
       <c r="F300">
-        <v>274</v>
+        <v>148</v>
       </c>
     </row>
     <row r="301">
@@ -16655,7 +16655,7 @@
         <v>High</v>
       </c>
       <c r="F301">
-        <v>225</v>
+        <v>198</v>
       </c>
     </row>
     <row r="302">
@@ -16675,7 +16675,7 @@
         <v>Medium</v>
       </c>
       <c r="F302">
-        <v>143</v>
+        <v>203</v>
       </c>
     </row>
     <row r="303">
@@ -16695,7 +16695,7 @@
         <v>Medium</v>
       </c>
       <c r="F303">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="304">
@@ -16715,7 +16715,7 @@
         <v>Medium</v>
       </c>
       <c r="F304">
-        <v>275</v>
+        <v>224</v>
       </c>
     </row>
     <row r="305">
@@ -16735,7 +16735,7 @@
         <v>High</v>
       </c>
       <c r="F305">
-        <v>184</v>
+        <v>255</v>
       </c>
     </row>
     <row r="306">
@@ -16755,7 +16755,7 @@
         <v>Medium</v>
       </c>
       <c r="F306">
-        <v>126</v>
+        <v>103</v>
       </c>
     </row>
     <row r="307">
@@ -16775,7 +16775,7 @@
         <v>Medium</v>
       </c>
       <c r="F307">
-        <v>200</v>
+        <v>246</v>
       </c>
     </row>
     <row r="308">
@@ -16795,7 +16795,7 @@
         <v>Medium</v>
       </c>
       <c r="F308">
-        <v>173</v>
+        <v>214</v>
       </c>
     </row>
     <row r="309">
@@ -16815,7 +16815,7 @@
         <v>High</v>
       </c>
       <c r="F309">
-        <v>227</v>
+        <v>113</v>
       </c>
     </row>
     <row r="310">
@@ -16835,7 +16835,7 @@
         <v>Medium</v>
       </c>
       <c r="F310">
-        <v>263</v>
+        <v>115</v>
       </c>
     </row>
     <row r="311">
@@ -16855,7 +16855,7 @@
         <v>Medium</v>
       </c>
       <c r="F311">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="312">
@@ -16875,7 +16875,7 @@
         <v>Medium</v>
       </c>
       <c r="F312">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
     <row r="313">
@@ -16895,7 +16895,7 @@
         <v>High</v>
       </c>
       <c r="F313">
-        <v>221</v>
+        <v>260</v>
       </c>
     </row>
     <row r="314">
@@ -16915,7 +16915,7 @@
         <v>Medium</v>
       </c>
       <c r="F314">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="315">
@@ -16935,7 +16935,7 @@
         <v>Medium</v>
       </c>
       <c r="F315">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="316">
@@ -16955,7 +16955,7 @@
         <v>Medium</v>
       </c>
       <c r="F316">
-        <v>107</v>
+        <v>201</v>
       </c>
     </row>
     <row r="317">
@@ -16975,7 +16975,7 @@
         <v>High</v>
       </c>
       <c r="F317">
-        <v>125</v>
+        <v>95</v>
       </c>
     </row>
     <row r="318">
@@ -16995,7 +16995,7 @@
         <v>Medium</v>
       </c>
       <c r="F318">
-        <v>225</v>
+        <v>257</v>
       </c>
     </row>
     <row r="319">
@@ -17015,7 +17015,7 @@
         <v>Medium</v>
       </c>
       <c r="F319">
-        <v>208</v>
+        <v>259</v>
       </c>
     </row>
     <row r="320">
@@ -17035,7 +17035,7 @@
         <v>Medium</v>
       </c>
       <c r="F320">
-        <v>254</v>
+        <v>212</v>
       </c>
     </row>
     <row r="321">
@@ -17055,7 +17055,7 @@
         <v>High</v>
       </c>
       <c r="F321">
-        <v>233</v>
+        <v>179</v>
       </c>
     </row>
     <row r="322">
@@ -17075,7 +17075,7 @@
         <v>Medium</v>
       </c>
       <c r="F322">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="323">
@@ -17095,7 +17095,7 @@
         <v>Medium</v>
       </c>
       <c r="F323">
-        <v>201</v>
+        <v>158</v>
       </c>
     </row>
     <row r="324">
@@ -17115,7 +17115,7 @@
         <v>Medium</v>
       </c>
       <c r="F324">
-        <v>134</v>
+        <v>198</v>
       </c>
     </row>
     <row r="325">
@@ -17135,7 +17135,7 @@
         <v>High</v>
       </c>
       <c r="F325">
-        <v>217</v>
+        <v>173</v>
       </c>
     </row>
     <row r="326">
@@ -17155,7 +17155,7 @@
         <v>Medium</v>
       </c>
       <c r="F326">
-        <v>204</v>
+        <v>273</v>
       </c>
     </row>
     <row r="327">
@@ -17175,7 +17175,7 @@
         <v>Medium</v>
       </c>
       <c r="F327">
-        <v>242</v>
+        <v>138</v>
       </c>
     </row>
     <row r="328">
@@ -17195,7 +17195,7 @@
         <v>Medium</v>
       </c>
       <c r="F328">
-        <v>248</v>
+        <v>102</v>
       </c>
     </row>
     <row r="329">
@@ -17215,7 +17215,7 @@
         <v>High</v>
       </c>
       <c r="F329">
-        <v>137</v>
+        <v>208</v>
       </c>
     </row>
     <row r="330">
@@ -17235,7 +17235,7 @@
         <v>Medium</v>
       </c>
       <c r="F330">
-        <v>135</v>
+        <v>248</v>
       </c>
     </row>
     <row r="331">
@@ -17255,7 +17255,7 @@
         <v>Medium</v>
       </c>
       <c r="F331">
-        <v>176</v>
+        <v>151</v>
       </c>
     </row>
     <row r="332">
@@ -17275,7 +17275,7 @@
         <v>Medium</v>
       </c>
       <c r="F332">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="333">
@@ -17295,7 +17295,7 @@
         <v>High</v>
       </c>
       <c r="F333">
-        <v>82</v>
+        <v>186</v>
       </c>
     </row>
     <row r="334">
@@ -17315,7 +17315,7 @@
         <v>Medium</v>
       </c>
       <c r="F334">
-        <v>206</v>
+        <v>252</v>
       </c>
     </row>
     <row r="335">
@@ -17335,7 +17335,7 @@
         <v>Medium</v>
       </c>
       <c r="F335">
-        <v>107</v>
+        <v>255</v>
       </c>
     </row>
     <row r="336">
@@ -17355,7 +17355,7 @@
         <v>Medium</v>
       </c>
       <c r="F336">
-        <v>179</v>
+        <v>103</v>
       </c>
     </row>
     <row r="337">
@@ -17375,7 +17375,7 @@
         <v>High</v>
       </c>
       <c r="F337">
-        <v>213</v>
+        <v>175</v>
       </c>
     </row>
     <row r="338">
@@ -17395,7 +17395,7 @@
         <v>Medium</v>
       </c>
       <c r="F338">
-        <v>96</v>
+        <v>238</v>
       </c>
     </row>
     <row r="339">
@@ -17415,7 +17415,7 @@
         <v>Medium</v>
       </c>
       <c r="F339">
-        <v>98</v>
+        <v>253</v>
       </c>
     </row>
     <row r="340">
@@ -17435,7 +17435,7 @@
         <v>Medium</v>
       </c>
       <c r="F340">
-        <v>158</v>
+        <v>192</v>
       </c>
     </row>
     <row r="341">
@@ -17455,7 +17455,7 @@
         <v>High</v>
       </c>
       <c r="F341">
-        <v>260</v>
+        <v>173</v>
       </c>
     </row>
     <row r="342">
@@ -17475,7 +17475,7 @@
         <v>Medium</v>
       </c>
       <c r="F342">
-        <v>247</v>
+        <v>226</v>
       </c>
     </row>
     <row r="343">
@@ -17495,7 +17495,7 @@
         <v>Medium</v>
       </c>
       <c r="F343">
-        <v>95</v>
+        <v>221</v>
       </c>
     </row>
     <row r="344">
@@ -17515,7 +17515,7 @@
         <v>Medium</v>
       </c>
       <c r="F344">
-        <v>275</v>
+        <v>106</v>
       </c>
     </row>
     <row r="345">
@@ -17535,7 +17535,7 @@
         <v>High</v>
       </c>
       <c r="F345">
-        <v>110</v>
+        <v>221</v>
       </c>
     </row>
     <row r="346">
@@ -17555,7 +17555,7 @@
         <v>Medium</v>
       </c>
       <c r="F346">
-        <v>137</v>
+        <v>174</v>
       </c>
     </row>
     <row r="347">
@@ -17575,7 +17575,7 @@
         <v>Medium</v>
       </c>
       <c r="F347">
-        <v>271</v>
+        <v>166</v>
       </c>
     </row>
     <row r="348">
@@ -17595,7 +17595,7 @@
         <v>Medium</v>
       </c>
       <c r="F348">
-        <v>81</v>
+        <v>188</v>
       </c>
     </row>
     <row r="349">
@@ -17615,7 +17615,7 @@
         <v>High</v>
       </c>
       <c r="F349">
-        <v>113</v>
+        <v>202</v>
       </c>
     </row>
     <row r="350">
@@ -17635,7 +17635,7 @@
         <v>Medium</v>
       </c>
       <c r="F350">
-        <v>146</v>
+        <v>109</v>
       </c>
     </row>
     <row r="351">
@@ -17655,7 +17655,7 @@
         <v>Medium</v>
       </c>
       <c r="F351">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="352">
@@ -17675,7 +17675,7 @@
         <v>Medium</v>
       </c>
       <c r="F352">
-        <v>235</v>
+        <v>220</v>
       </c>
     </row>
     <row r="353">
@@ -17695,7 +17695,7 @@
         <v>High</v>
       </c>
       <c r="F353">
-        <v>269</v>
+        <v>166</v>
       </c>
     </row>
     <row r="354">
@@ -17715,7 +17715,7 @@
         <v>Medium</v>
       </c>
       <c r="F354">
-        <v>245</v>
+        <v>154</v>
       </c>
     </row>
     <row r="355">
@@ -17735,7 +17735,7 @@
         <v>Medium</v>
       </c>
       <c r="F355">
-        <v>157</v>
+        <v>110</v>
       </c>
     </row>
     <row r="356">
@@ -17755,7 +17755,7 @@
         <v>Medium</v>
       </c>
       <c r="F356">
-        <v>173</v>
+        <v>261</v>
       </c>
     </row>
     <row r="357">
@@ -17775,7 +17775,7 @@
         <v>High</v>
       </c>
       <c r="F357">
-        <v>245</v>
+        <v>143</v>
       </c>
     </row>
     <row r="358">
@@ -17795,7 +17795,7 @@
         <v>Medium</v>
       </c>
       <c r="F358">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="359">
@@ -17815,7 +17815,7 @@
         <v>Medium</v>
       </c>
       <c r="F359">
-        <v>258</v>
+        <v>227</v>
       </c>
     </row>
     <row r="360">
@@ -17835,7 +17835,7 @@
         <v>Medium</v>
       </c>
       <c r="F360">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="361">
@@ -17855,7 +17855,7 @@
         <v>High</v>
       </c>
       <c r="F361">
-        <v>277</v>
+        <v>245</v>
       </c>
     </row>
     <row r="362">
@@ -17875,7 +17875,7 @@
         <v>Medium</v>
       </c>
       <c r="F362">
-        <v>118</v>
+        <v>195</v>
       </c>
     </row>
     <row r="363">
@@ -17895,7 +17895,7 @@
         <v>Medium</v>
       </c>
       <c r="F363">
-        <v>95</v>
+        <v>200</v>
       </c>
     </row>
     <row r="364">
@@ -17915,7 +17915,7 @@
         <v>Medium</v>
       </c>
       <c r="F364">
-        <v>204</v>
+        <v>121</v>
       </c>
     </row>
     <row r="365">
@@ -17935,7 +17935,7 @@
         <v>High</v>
       </c>
       <c r="F365">
-        <v>194</v>
+        <v>163</v>
       </c>
     </row>
     <row r="366">
@@ -17955,7 +17955,7 @@
         <v>Medium</v>
       </c>
       <c r="F366">
-        <v>211</v>
+        <v>101</v>
       </c>
     </row>
     <row r="367">
@@ -17975,7 +17975,7 @@
         <v>Medium</v>
       </c>
       <c r="F367">
-        <v>147</v>
+        <v>238</v>
       </c>
     </row>
     <row r="368">
@@ -17995,7 +17995,7 @@
         <v>Medium</v>
       </c>
       <c r="F368">
-        <v>249</v>
+        <v>128</v>
       </c>
     </row>
     <row r="369">
@@ -18015,7 +18015,7 @@
         <v>High</v>
       </c>
       <c r="F369">
-        <v>203</v>
+        <v>232</v>
       </c>
     </row>
     <row r="370">
@@ -18035,7 +18035,7 @@
         <v>Medium</v>
       </c>
       <c r="F370">
-        <v>147</v>
+        <v>122</v>
       </c>
     </row>
     <row r="371">
@@ -18055,7 +18055,7 @@
         <v>Medium</v>
       </c>
       <c r="F371">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="372">
@@ -18075,7 +18075,7 @@
         <v>Medium</v>
       </c>
       <c r="F372">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
     <row r="373">
@@ -18095,7 +18095,7 @@
         <v>High</v>
       </c>
       <c r="F373">
-        <v>206</v>
+        <v>164</v>
       </c>
     </row>
     <row r="374">
@@ -18115,7 +18115,7 @@
         <v>Medium</v>
       </c>
       <c r="F374">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="375">
@@ -18155,7 +18155,7 @@
         <v>Medium</v>
       </c>
       <c r="F376">
-        <v>105</v>
+        <v>248</v>
       </c>
     </row>
     <row r="377">
@@ -18175,7 +18175,7 @@
         <v>High</v>
       </c>
       <c r="F377">
-        <v>175</v>
+        <v>246</v>
       </c>
     </row>
     <row r="378">
@@ -18195,7 +18195,7 @@
         <v>Medium</v>
       </c>
       <c r="F378">
-        <v>159</v>
+        <v>276</v>
       </c>
     </row>
     <row r="379">
@@ -18215,7 +18215,7 @@
         <v>Medium</v>
       </c>
       <c r="F379">
-        <v>224</v>
+        <v>194</v>
       </c>
     </row>
     <row r="380">
@@ -18235,7 +18235,7 @@
         <v>Medium</v>
       </c>
       <c r="F380">
-        <v>173</v>
+        <v>216</v>
       </c>
     </row>
     <row r="381">
@@ -18255,7 +18255,7 @@
         <v>High</v>
       </c>
       <c r="F381">
-        <v>150</v>
+        <v>192</v>
       </c>
     </row>
     <row r="382">
@@ -18275,7 +18275,7 @@
         <v>Medium</v>
       </c>
       <c r="F382">
-        <v>252</v>
+        <v>233</v>
       </c>
     </row>
     <row r="383">
@@ -18295,7 +18295,7 @@
         <v>Medium</v>
       </c>
       <c r="F383">
-        <v>110</v>
+        <v>251</v>
       </c>
     </row>
     <row r="384">
@@ -18315,7 +18315,7 @@
         <v>Medium</v>
       </c>
       <c r="F384">
-        <v>125</v>
+        <v>174</v>
       </c>
     </row>
     <row r="385">
@@ -18335,7 +18335,7 @@
         <v>High</v>
       </c>
       <c r="F385">
-        <v>116</v>
+        <v>255</v>
       </c>
     </row>
     <row r="386">
@@ -18355,7 +18355,7 @@
         <v>Medium</v>
       </c>
       <c r="F386">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="387">
@@ -18375,7 +18375,7 @@
         <v>Medium</v>
       </c>
       <c r="F387">
-        <v>137</v>
+        <v>262</v>
       </c>
     </row>
     <row r="388">
@@ -18395,7 +18395,7 @@
         <v>Medium</v>
       </c>
       <c r="F388">
-        <v>276</v>
+        <v>145</v>
       </c>
     </row>
     <row r="389">
@@ -18415,7 +18415,7 @@
         <v>High</v>
       </c>
       <c r="F389">
-        <v>215</v>
+        <v>250</v>
       </c>
     </row>
     <row r="390">
@@ -18435,7 +18435,7 @@
         <v>Medium</v>
       </c>
       <c r="F390">
-        <v>237</v>
+        <v>120</v>
       </c>
     </row>
     <row r="391">
@@ -18455,7 +18455,7 @@
         <v>Medium</v>
       </c>
       <c r="F391">
-        <v>246</v>
+        <v>92</v>
       </c>
     </row>
     <row r="392">
@@ -18475,7 +18475,7 @@
         <v>Medium</v>
       </c>
       <c r="F392">
-        <v>164</v>
+        <v>250</v>
       </c>
     </row>
     <row r="393">
@@ -18495,7 +18495,7 @@
         <v>High</v>
       </c>
       <c r="F393">
-        <v>242</v>
+        <v>159</v>
       </c>
     </row>
     <row r="394">
@@ -18515,7 +18515,7 @@
         <v>Medium</v>
       </c>
       <c r="F394">
-        <v>145</v>
+        <v>259</v>
       </c>
     </row>
     <row r="395">
@@ -18535,7 +18535,7 @@
         <v>Medium</v>
       </c>
       <c r="F395">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="396">
@@ -18555,7 +18555,7 @@
         <v>Medium</v>
       </c>
       <c r="F396">
-        <v>175</v>
+        <v>275</v>
       </c>
     </row>
     <row r="397">
@@ -18575,7 +18575,7 @@
         <v>High</v>
       </c>
       <c r="F397">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="398">
@@ -18595,7 +18595,7 @@
         <v>Medium</v>
       </c>
       <c r="F398">
-        <v>165</v>
+        <v>251</v>
       </c>
     </row>
     <row r="399">
@@ -18615,7 +18615,7 @@
         <v>Medium</v>
       </c>
       <c r="F399">
-        <v>254</v>
+        <v>175</v>
       </c>
     </row>
     <row r="400">
@@ -18635,7 +18635,7 @@
         <v>Medium</v>
       </c>
       <c r="F400">
-        <v>196</v>
+        <v>255</v>
       </c>
     </row>
     <row r="401">
@@ -18655,7 +18655,7 @@
         <v>High</v>
       </c>
       <c r="F401">
-        <v>242</v>
+        <v>213</v>
       </c>
     </row>
     <row r="402">
@@ -18675,7 +18675,7 @@
         <v>Medium</v>
       </c>
       <c r="F402">
-        <v>244</v>
+        <v>116</v>
       </c>
     </row>
     <row r="403">
@@ -18695,7 +18695,7 @@
         <v>Medium</v>
       </c>
       <c r="F403">
-        <v>257</v>
+        <v>159</v>
       </c>
     </row>
     <row r="404">
@@ -18715,7 +18715,7 @@
         <v>Medium</v>
       </c>
       <c r="F404">
-        <v>224</v>
+        <v>143</v>
       </c>
     </row>
     <row r="405">
@@ -18735,7 +18735,7 @@
         <v>High</v>
       </c>
       <c r="F405">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="406">
@@ -18755,7 +18755,7 @@
         <v>Medium</v>
       </c>
       <c r="F406">
-        <v>128</v>
+        <v>95</v>
       </c>
     </row>
     <row r="407">
@@ -18775,7 +18775,7 @@
         <v>Medium</v>
       </c>
       <c r="F407">
-        <v>242</v>
+        <v>109</v>
       </c>
     </row>
     <row r="408">
@@ -18795,7 +18795,7 @@
         <v>Medium</v>
       </c>
       <c r="F408">
-        <v>221</v>
+        <v>192</v>
       </c>
     </row>
     <row r="409">
@@ -18815,7 +18815,7 @@
         <v>High</v>
       </c>
       <c r="F409">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="410">
@@ -18835,7 +18835,7 @@
         <v>Medium</v>
       </c>
       <c r="F410">
-        <v>92</v>
+        <v>148</v>
       </c>
     </row>
     <row r="411">
@@ -18855,7 +18855,7 @@
         <v>Medium</v>
       </c>
       <c r="F411">
-        <v>103</v>
+        <v>235</v>
       </c>
     </row>
     <row r="412">
@@ -18875,7 +18875,7 @@
         <v>Medium</v>
       </c>
       <c r="F412">
-        <v>242</v>
+        <v>187</v>
       </c>
     </row>
     <row r="413">
@@ -18895,7 +18895,7 @@
         <v>Medium</v>
       </c>
       <c r="F413">
-        <v>237</v>
+        <v>146</v>
       </c>
     </row>
     <row r="414">
@@ -18915,7 +18915,7 @@
         <v>Medium</v>
       </c>
       <c r="F414">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="415">
@@ -18935,7 +18935,7 @@
         <v>High</v>
       </c>
       <c r="F415">
-        <v>187</v>
+        <v>233</v>
       </c>
     </row>
     <row r="416">
@@ -18955,7 +18955,7 @@
         <v>Medium</v>
       </c>
       <c r="F416">
-        <v>197</v>
+        <v>99</v>
       </c>
     </row>
     <row r="417">
@@ -18975,7 +18975,7 @@
         <v>Medium</v>
       </c>
       <c r="F417">
-        <v>163</v>
+        <v>230</v>
       </c>
     </row>
     <row r="418">
@@ -18995,7 +18995,7 @@
         <v>Medium</v>
       </c>
       <c r="F418">
-        <v>243</v>
+        <v>116</v>
       </c>
     </row>
     <row r="419">
@@ -19015,7 +19015,7 @@
         <v>High</v>
       </c>
       <c r="F419">
-        <v>132</v>
+        <v>166</v>
       </c>
     </row>
     <row r="420">
@@ -19035,7 +19035,7 @@
         <v>Medium</v>
       </c>
       <c r="F420">
-        <v>240</v>
+        <v>93</v>
       </c>
     </row>
     <row r="421">
@@ -19055,7 +19055,7 @@
         <v>Medium</v>
       </c>
       <c r="F421">
-        <v>137</v>
+        <v>223</v>
       </c>
     </row>
     <row r="422">
@@ -19075,7 +19075,7 @@
         <v>Medium</v>
       </c>
       <c r="F422">
-        <v>196</v>
+        <v>94</v>
       </c>
     </row>
     <row r="423">
@@ -19095,7 +19095,7 @@
         <v>High</v>
       </c>
       <c r="F423">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="424">
@@ -19115,7 +19115,7 @@
         <v>Medium</v>
       </c>
       <c r="F424">
-        <v>237</v>
+        <v>174</v>
       </c>
     </row>
     <row r="425">
@@ -19135,7 +19135,7 @@
         <v>Medium</v>
       </c>
       <c r="F425">
-        <v>134</v>
+        <v>111</v>
       </c>
     </row>
     <row r="426">
@@ -19155,7 +19155,7 @@
         <v>Medium</v>
       </c>
       <c r="F426">
-        <v>100</v>
+        <v>176</v>
       </c>
     </row>
     <row r="427">
@@ -19175,7 +19175,7 @@
         <v>High</v>
       </c>
       <c r="F427">
-        <v>163</v>
+        <v>226</v>
       </c>
     </row>
     <row r="428">
@@ -19195,7 +19195,7 @@
         <v>Medium</v>
       </c>
       <c r="F428">
-        <v>179</v>
+        <v>124</v>
       </c>
     </row>
     <row r="429">
@@ -19215,7 +19215,7 @@
         <v>Medium</v>
       </c>
       <c r="F429">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="430">
@@ -19235,7 +19235,7 @@
         <v>Medium</v>
       </c>
       <c r="F430">
-        <v>149</v>
+        <v>225</v>
       </c>
     </row>
     <row r="431">
@@ -19255,7 +19255,7 @@
         <v>High</v>
       </c>
       <c r="F431">
-        <v>132</v>
+        <v>198</v>
       </c>
     </row>
     <row r="432">
@@ -19275,7 +19275,7 @@
         <v>Medium</v>
       </c>
       <c r="F432">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="433">
@@ -19295,7 +19295,7 @@
         <v>Medium</v>
       </c>
       <c r="F433">
-        <v>163</v>
+        <v>235</v>
       </c>
     </row>
     <row r="434">
@@ -19315,7 +19315,7 @@
         <v>Medium</v>
       </c>
       <c r="F434">
-        <v>264</v>
+        <v>165</v>
       </c>
     </row>
     <row r="435">
@@ -19335,7 +19335,7 @@
         <v>High</v>
       </c>
       <c r="F435">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="436">
@@ -19355,7 +19355,7 @@
         <v>Medium</v>
       </c>
       <c r="F436">
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="437">
@@ -19375,7 +19375,7 @@
         <v>Medium</v>
       </c>
       <c r="F437">
-        <v>162</v>
+        <v>199</v>
       </c>
     </row>
     <row r="438">
@@ -19395,7 +19395,7 @@
         <v>Medium</v>
       </c>
       <c r="F438">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="439">
@@ -19415,7 +19415,7 @@
         <v>High</v>
       </c>
       <c r="F439">
-        <v>157</v>
+        <v>251</v>
       </c>
     </row>
     <row r="440">
@@ -19435,7 +19435,7 @@
         <v>Medium</v>
       </c>
       <c r="F440">
-        <v>210</v>
+        <v>123</v>
       </c>
     </row>
     <row r="441">
@@ -19455,7 +19455,7 @@
         <v>Medium</v>
       </c>
       <c r="F441">
-        <v>212</v>
+        <v>171</v>
       </c>
     </row>
     <row r="442">
@@ -19475,7 +19475,7 @@
         <v>Medium</v>
       </c>
       <c r="F442">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="443">
@@ -19495,7 +19495,7 @@
         <v>Medium</v>
       </c>
       <c r="F443">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="444">
@@ -19515,7 +19515,7 @@
         <v>Medium</v>
       </c>
       <c r="F444">
-        <v>208</v>
+        <v>138</v>
       </c>
     </row>
     <row r="445">
@@ -19535,7 +19535,7 @@
         <v>High</v>
       </c>
       <c r="F445">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="446">
@@ -19555,7 +19555,7 @@
         <v>Medium</v>
       </c>
       <c r="F446">
-        <v>198</v>
+        <v>233</v>
       </c>
     </row>
     <row r="447">
@@ -19575,7 +19575,7 @@
         <v>Medium</v>
       </c>
       <c r="F447">
-        <v>217</v>
+        <v>261</v>
       </c>
     </row>
     <row r="448">
@@ -19595,7 +19595,7 @@
         <v>Medium</v>
       </c>
       <c r="F448">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="449">
@@ -19615,7 +19615,7 @@
         <v>High</v>
       </c>
       <c r="F449">
-        <v>112</v>
+        <v>271</v>
       </c>
     </row>
     <row r="450">
@@ -19635,7 +19635,7 @@
         <v>Medium</v>
       </c>
       <c r="F450">
-        <v>196</v>
+        <v>241</v>
       </c>
     </row>
     <row r="451">
@@ -19655,7 +19655,7 @@
         <v>Medium</v>
       </c>
       <c r="F451">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452">
@@ -19675,7 +19675,7 @@
         <v>Medium</v>
       </c>
       <c r="F452">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="453">
@@ -19695,7 +19695,7 @@
         <v>High</v>
       </c>
       <c r="F453">
-        <v>182</v>
+        <v>229</v>
       </c>
     </row>
     <row r="454">
@@ -19715,7 +19715,7 @@
         <v>Medium</v>
       </c>
       <c r="F454">
-        <v>198</v>
+        <v>106</v>
       </c>
     </row>
     <row r="455">
@@ -19735,7 +19735,7 @@
         <v>Medium</v>
       </c>
       <c r="F455">
-        <v>204</v>
+        <v>153</v>
       </c>
     </row>
     <row r="456">
@@ -19755,7 +19755,7 @@
         <v>Medium</v>
       </c>
       <c r="F456">
-        <v>145</v>
+        <v>220</v>
       </c>
     </row>
     <row r="457">
@@ -19775,7 +19775,7 @@
         <v>High</v>
       </c>
       <c r="F457">
-        <v>101</v>
+        <v>198</v>
       </c>
     </row>
     <row r="458">
@@ -19795,7 +19795,7 @@
         <v>Medium</v>
       </c>
       <c r="F458">
-        <v>276</v>
+        <v>218</v>
       </c>
     </row>
     <row r="459">
@@ -19815,7 +19815,7 @@
         <v>Medium</v>
       </c>
       <c r="F459">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="460">
@@ -19835,7 +19835,7 @@
         <v>Medium</v>
       </c>
       <c r="F460">
-        <v>275</v>
+        <v>241</v>
       </c>
     </row>
     <row r="461">
@@ -19855,7 +19855,7 @@
         <v>High</v>
       </c>
       <c r="F461">
-        <v>164</v>
+        <v>219</v>
       </c>
     </row>
     <row r="462">
@@ -19875,7 +19875,7 @@
         <v>Medium</v>
       </c>
       <c r="F462">
-        <v>220</v>
+        <v>140</v>
       </c>
     </row>
     <row r="463">
@@ -19895,7 +19895,7 @@
         <v>Medium</v>
       </c>
       <c r="F463">
-        <v>239</v>
+        <v>107</v>
       </c>
     </row>
     <row r="464">
@@ -19915,7 +19915,7 @@
         <v>Medium</v>
       </c>
       <c r="F464">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="465">
@@ -19935,7 +19935,7 @@
         <v>High</v>
       </c>
       <c r="F465">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="466">
@@ -19955,7 +19955,7 @@
         <v>Medium</v>
       </c>
       <c r="F466">
-        <v>87</v>
+        <v>182</v>
       </c>
     </row>
     <row r="467">
@@ -19975,7 +19975,7 @@
         <v>Medium</v>
       </c>
       <c r="F467">
-        <v>212</v>
+        <v>243</v>
       </c>
     </row>
     <row r="468">
@@ -19995,7 +19995,7 @@
         <v>Medium</v>
       </c>
       <c r="F468">
-        <v>133</v>
+        <v>205</v>
       </c>
     </row>
     <row r="469">
@@ -20015,7 +20015,7 @@
         <v>High</v>
       </c>
       <c r="F469">
-        <v>214</v>
+        <v>85</v>
       </c>
     </row>
     <row r="470">
@@ -20035,7 +20035,7 @@
         <v>Medium</v>
       </c>
       <c r="F470">
-        <v>148</v>
+        <v>119</v>
       </c>
     </row>
     <row r="471">
@@ -20055,7 +20055,7 @@
         <v>Medium</v>
       </c>
       <c r="F471">
-        <v>243</v>
+        <v>137</v>
       </c>
     </row>
     <row r="472">
@@ -20075,7 +20075,7 @@
         <v>Medium</v>
       </c>
       <c r="F472">
-        <v>182</v>
+        <v>253</v>
       </c>
     </row>
     <row r="473">
@@ -20095,7 +20095,7 @@
         <v>High</v>
       </c>
       <c r="F473">
-        <v>222</v>
+        <v>89</v>
       </c>
     </row>
     <row r="474">
@@ -20115,7 +20115,7 @@
         <v>Medium</v>
       </c>
       <c r="F474">
-        <v>259</v>
+        <v>240</v>
       </c>
     </row>
     <row r="475">
@@ -20135,7 +20135,7 @@
         <v>Medium</v>
       </c>
       <c r="F475">
-        <v>151</v>
+        <v>277</v>
       </c>
     </row>
     <row r="476">
@@ -20155,7 +20155,7 @@
         <v>Medium</v>
       </c>
       <c r="F476">
-        <v>108</v>
+        <v>115</v>
       </c>
     </row>
     <row r="477">
@@ -20175,7 +20175,7 @@
         <v>High</v>
       </c>
       <c r="F477">
-        <v>161</v>
+        <v>96</v>
       </c>
     </row>
     <row r="478">
@@ -20195,7 +20195,7 @@
         <v>Medium</v>
       </c>
       <c r="F478">
-        <v>264</v>
+        <v>92</v>
       </c>
     </row>
     <row r="479">
@@ -20215,7 +20215,7 @@
         <v>Medium</v>
       </c>
       <c r="F479">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="480">
@@ -20235,7 +20235,7 @@
         <v>Medium</v>
       </c>
       <c r="F480">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="481">
@@ -20255,7 +20255,7 @@
         <v>High</v>
       </c>
       <c r="F481">
-        <v>92</v>
+        <v>254</v>
       </c>
     </row>
     <row r="482">
@@ -20275,7 +20275,7 @@
         <v>Medium</v>
       </c>
       <c r="F482">
-        <v>267</v>
+        <v>138</v>
       </c>
     </row>
     <row r="483">
@@ -20295,7 +20295,7 @@
         <v>Medium</v>
       </c>
       <c r="F483">
-        <v>180</v>
+        <v>147</v>
       </c>
     </row>
     <row r="484">
@@ -20315,7 +20315,7 @@
         <v>Medium</v>
       </c>
       <c r="F484">
-        <v>245</v>
+        <v>145</v>
       </c>
     </row>
     <row r="485">
@@ -20335,7 +20335,7 @@
         <v>High</v>
       </c>
       <c r="F485">
-        <v>157</v>
+        <v>247</v>
       </c>
     </row>
     <row r="486">
@@ -20355,7 +20355,7 @@
         <v>Medium</v>
       </c>
       <c r="F486">
-        <v>232</v>
+        <v>95</v>
       </c>
     </row>
     <row r="487">
@@ -20375,7 +20375,7 @@
         <v>Medium</v>
       </c>
       <c r="F487">
-        <v>112</v>
+        <v>226</v>
       </c>
     </row>
     <row r="488">
@@ -20395,7 +20395,7 @@
         <v>Medium</v>
       </c>
       <c r="F488">
-        <v>139</v>
+        <v>99</v>
       </c>
     </row>
     <row r="489">
@@ -20415,7 +20415,7 @@
         <v>High</v>
       </c>
       <c r="F489">
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="490">
@@ -20435,7 +20435,7 @@
         <v>Medium</v>
       </c>
       <c r="F490">
-        <v>81</v>
+        <v>182</v>
       </c>
     </row>
     <row r="491">
@@ -20455,7 +20455,7 @@
         <v>Medium</v>
       </c>
       <c r="F491">
-        <v>184</v>
+        <v>98</v>
       </c>
     </row>
     <row r="492">
@@ -20475,7 +20475,7 @@
         <v>Medium</v>
       </c>
       <c r="F492">
-        <v>124</v>
+        <v>204</v>
       </c>
     </row>
     <row r="493">
@@ -20495,7 +20495,7 @@
         <v>High</v>
       </c>
       <c r="F493">
-        <v>189</v>
+        <v>154</v>
       </c>
     </row>
     <row r="494">
@@ -20515,7 +20515,7 @@
         <v>Medium</v>
       </c>
       <c r="F494">
-        <v>174</v>
+        <v>264</v>
       </c>
     </row>
     <row r="495">
@@ -20535,7 +20535,7 @@
         <v>Medium</v>
       </c>
       <c r="F495">
-        <v>141</v>
+        <v>102</v>
       </c>
     </row>
     <row r="496">
@@ -20555,7 +20555,7 @@
         <v>Medium</v>
       </c>
       <c r="F496">
-        <v>174</v>
+        <v>246</v>
       </c>
     </row>
     <row r="497">
@@ -20575,7 +20575,7 @@
         <v>High</v>
       </c>
       <c r="F497">
-        <v>112</v>
+        <v>141</v>
       </c>
     </row>
     <row r="498">
@@ -20595,7 +20595,7 @@
         <v>Medium</v>
       </c>
       <c r="F498">
-        <v>149</v>
+        <v>183</v>
       </c>
     </row>
     <row r="499">
@@ -20615,7 +20615,7 @@
         <v>Medium</v>
       </c>
       <c r="F499">
-        <v>123</v>
+        <v>90</v>
       </c>
     </row>
     <row r="500">
@@ -20635,7 +20635,7 @@
         <v>Medium</v>
       </c>
       <c r="F500">
-        <v>248</v>
+        <v>159</v>
       </c>
     </row>
     <row r="501">
@@ -20655,7 +20655,7 @@
         <v>High</v>
       </c>
       <c r="F501">
-        <v>90</v>
+        <v>185</v>
       </c>
     </row>
     <row r="502">
@@ -20675,7 +20675,7 @@
         <v>Medium</v>
       </c>
       <c r="F502">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="503">
@@ -20695,7 +20695,7 @@
         <v>Medium</v>
       </c>
       <c r="F503">
-        <v>161</v>
+        <v>272</v>
       </c>
     </row>
     <row r="504">
@@ -20715,7 +20715,7 @@
         <v>Medium</v>
       </c>
       <c r="F504">
-        <v>240</v>
+        <v>154</v>
       </c>
     </row>
     <row r="505">
@@ -20735,7 +20735,7 @@
         <v>High</v>
       </c>
       <c r="F505">
-        <v>89</v>
+        <v>97</v>
       </c>
     </row>
     <row r="506">
@@ -20755,7 +20755,7 @@
         <v>Medium</v>
       </c>
       <c r="F506">
-        <v>93</v>
+        <v>166</v>
       </c>
     </row>
     <row r="507">
@@ -20775,7 +20775,7 @@
         <v>Medium</v>
       </c>
       <c r="F507">
-        <v>162</v>
+        <v>265</v>
       </c>
     </row>
     <row r="508">
@@ -20795,7 +20795,7 @@
         <v>Medium</v>
       </c>
       <c r="F508">
-        <v>248</v>
+        <v>82</v>
       </c>
     </row>
     <row r="509">
@@ -20815,7 +20815,7 @@
         <v>High</v>
       </c>
       <c r="F509">
-        <v>120</v>
+        <v>274</v>
       </c>
     </row>
     <row r="510">
@@ -20835,7 +20835,7 @@
         <v>Medium</v>
       </c>
       <c r="F510">
-        <v>82</v>
+        <v>187</v>
       </c>
     </row>
     <row r="511">
@@ -20855,7 +20855,7 @@
         <v>Medium</v>
       </c>
       <c r="F511">
-        <v>231</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
